--- a/Kingdom_4194_Live_Telemetry.xlsx
+++ b/Kingdom_4194_Live_Telemetry.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7278" uniqueCount="893">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7278" uniqueCount="892">
   <si>
     <t>Rank</t>
   </si>
@@ -388,7 +388,7 @@
     <t>{1:20112_1:0,2:20090_2:30,6:20086_0:0}</t>
   </si>
   <si>
-    <t>X:833.5 Y:6085.41</t>
+    <t>X:177.2 Y:992.8</t>
   </si>
   <si>
     <t>01D622E5E1EEE30A551499A520C8EE23</t>
@@ -685,7 +685,7 @@
     <t>{1:20100_2:30,2:20104_5:0,3:20084_4:0,4:20085_3:0,5:20101_0:30}</t>
   </si>
   <si>
-    <t>X:1117.62 Y:6006.27</t>
+    <t>X:186.3 Y:1001</t>
   </si>
   <si>
     <t>230922466639634154</t>
@@ -763,9 +763,6 @@
     <t>{3:20084_0:0,4:20085_1:0}</t>
   </si>
   <si>
-    <t>X:1113.07 Y:6109.47</t>
-  </si>
-  <si>
     <t>7B011AC2-5C35-4792-A86A-C535A9FE43E9</t>
   </si>
   <si>
@@ -826,7 +823,7 @@
     <t>{1:20087_13:0,2:20103_12:0,3:20106_7:0,6:20117_2:0}</t>
   </si>
   <si>
-    <t>X:1283.06 Y:5605.37</t>
+    <t>X:180.5 Y:952</t>
   </si>
   <si>
     <t>E3C0506672BDA7429F16031324D7E5EA</t>
@@ -1003,7 +1000,7 @@
     <t>{1:20100_8:30,2:20104_9:0,3:20084_7:0,5:20101_6:0,6:20110_4:0}</t>
   </si>
   <si>
-    <t>X:1567.35 Y:6281.53</t>
+    <t>X:146.1 Y:1014</t>
   </si>
   <si>
     <t>413842294543088168</t>
@@ -17010,31 +17007,31 @@
         <v>82</v>
       </c>
       <c r="BJ59" t="s">
-        <v>250</v>
+        <v>125</v>
       </c>
       <c r="BK59">
         <v>8454214</v>
       </c>
       <c r="BL59" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="BM59">
         <v>224313413</v>
       </c>
       <c r="BN59" t="s">
+        <v>251</v>
+      </c>
+      <c r="BO59" t="s">
         <v>252</v>
       </c>
-      <c r="BO59" t="s">
+      <c r="BP59" t="s">
         <v>253</v>
       </c>
-      <c r="BP59" t="s">
+      <c r="BQ59" t="s">
         <v>254</v>
       </c>
-      <c r="BQ59" t="s">
+      <c r="BR59" t="s">
         <v>255</v>
-      </c>
-      <c r="BR59" t="s">
-        <v>256</v>
       </c>
       <c r="BS59">
         <v>NaN</v>
@@ -17043,7 +17040,7 @@
         <v>82</v>
       </c>
       <c r="BU59" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="BV59">
         <v>3194</v>
@@ -17075,7 +17072,7 @@
         <v>235692597</v>
       </c>
       <c r="E60" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="F60" t="s">
         <v>89</v>
@@ -17311,7 +17308,7 @@
         <v>235362694</v>
       </c>
       <c r="E61" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="F61" t="s">
         <v>89</v>
@@ -17547,7 +17544,7 @@
         <v>235365218</v>
       </c>
       <c r="E62" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="F62" t="s">
         <v>89</v>
@@ -17783,7 +17780,7 @@
         <v>235692835</v>
       </c>
       <c r="E63" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="F63" t="s">
         <v>89</v>
@@ -17960,7 +17957,7 @@
         <v>0</v>
       </c>
       <c r="BL63" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="BM63">
         <v>105928772</v>
@@ -17969,16 +17966,16 @@
         <v>82</v>
       </c>
       <c r="BO63" t="s">
+        <v>262</v>
+      </c>
+      <c r="BP63" t="s">
+        <v>82</v>
+      </c>
+      <c r="BQ63" t="s">
         <v>263</v>
       </c>
-      <c r="BP63" t="s">
-        <v>82</v>
-      </c>
-      <c r="BQ63" t="s">
+      <c r="BR63" t="s">
         <v>264</v>
-      </c>
-      <c r="BR63" t="s">
-        <v>265</v>
       </c>
       <c r="BS63">
         <v>NaN</v>
@@ -18019,7 +18016,7 @@
         <v>235695521</v>
       </c>
       <c r="E64" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="F64" t="s">
         <v>89</v>
@@ -18196,7 +18193,7 @@
         <v>0</v>
       </c>
       <c r="BL64" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="BM64">
         <v>0</v>
@@ -18255,7 +18252,7 @@
         <v>235599021</v>
       </c>
       <c r="E65" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="F65" t="s">
         <v>119</v>
@@ -18408,49 +18405,49 @@
         <v>122</v>
       </c>
       <c r="BD65" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="BE65" t="s">
         <v>122</v>
       </c>
       <c r="BF65" t="s">
+        <v>269</v>
+      </c>
+      <c r="BG65" t="s">
+        <v>82</v>
+      </c>
+      <c r="BH65">
+        <v>0</v>
+      </c>
+      <c r="BI65" t="s">
+        <v>82</v>
+      </c>
+      <c r="BJ65" t="s">
         <v>270</v>
-      </c>
-      <c r="BG65" t="s">
-        <v>82</v>
-      </c>
-      <c r="BH65">
-        <v>0</v>
-      </c>
-      <c r="BI65" t="s">
-        <v>82</v>
-      </c>
-      <c r="BJ65" t="s">
-        <v>271</v>
       </c>
       <c r="BK65">
         <v>8493236</v>
       </c>
       <c r="BL65" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="BM65">
         <v>72752421</v>
       </c>
       <c r="BN65" t="s">
+        <v>272</v>
+      </c>
+      <c r="BO65" t="s">
         <v>273</v>
-      </c>
-      <c r="BO65" t="s">
-        <v>274</v>
       </c>
       <c r="BP65" t="s">
         <v>129</v>
       </c>
       <c r="BQ65" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="BR65" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="BS65">
         <v>NaN</v>
@@ -18459,7 +18456,7 @@
         <v>82</v>
       </c>
       <c r="BU65" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="BV65">
         <v>3194</v>
@@ -18491,7 +18488,7 @@
         <v>235387457</v>
       </c>
       <c r="E66" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="F66" t="s">
         <v>89</v>
@@ -18668,7 +18665,7 @@
         <v>0</v>
       </c>
       <c r="BL66" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="BM66">
         <v>28586038</v>
@@ -18677,7 +18674,7 @@
         <v>82</v>
       </c>
       <c r="BO66" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="BP66" t="s">
         <v>82</v>
@@ -18686,7 +18683,7 @@
         <v>229</v>
       </c>
       <c r="BR66" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="BS66">
         <v>NaN</v>
@@ -18727,7 +18724,7 @@
         <v>235379949</v>
       </c>
       <c r="E67" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="F67" t="s">
         <v>89</v>
@@ -18963,7 +18960,7 @@
         <v>235381322</v>
       </c>
       <c r="E68" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="F68" t="s">
         <v>89</v>
@@ -19190,16 +19187,16 @@
         <v>68</v>
       </c>
       <c r="B69" t="s">
+        <v>282</v>
+      </c>
+      <c r="C69" t="s">
         <v>283</v>
-      </c>
-      <c r="C69" t="s">
-        <v>284</v>
       </c>
       <c r="D69">
         <v>235713996</v>
       </c>
       <c r="E69" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="F69" t="s">
         <v>178</v>
@@ -19426,16 +19423,16 @@
         <v>69</v>
       </c>
       <c r="B70" t="s">
+        <v>282</v>
+      </c>
+      <c r="C70" t="s">
         <v>283</v>
-      </c>
-      <c r="C70" t="s">
-        <v>284</v>
       </c>
       <c r="D70">
         <v>235455149</v>
       </c>
       <c r="E70" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="F70" t="s">
         <v>89</v>
@@ -19662,16 +19659,16 @@
         <v>70</v>
       </c>
       <c r="B71" t="s">
+        <v>282</v>
+      </c>
+      <c r="C71" t="s">
         <v>283</v>
-      </c>
-      <c r="C71" t="s">
-        <v>284</v>
       </c>
       <c r="D71">
         <v>235375841</v>
       </c>
       <c r="E71" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="F71" t="s">
         <v>178</v>
@@ -19898,16 +19895,16 @@
         <v>71</v>
       </c>
       <c r="B72" t="s">
+        <v>282</v>
+      </c>
+      <c r="C72" t="s">
         <v>283</v>
-      </c>
-      <c r="C72" t="s">
-        <v>284</v>
       </c>
       <c r="D72">
         <v>235361866</v>
       </c>
       <c r="E72" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="F72" t="s">
         <v>89</v>
@@ -20084,7 +20081,7 @@
         <v>0</v>
       </c>
       <c r="BL72" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="BM72">
         <v>0</v>
@@ -20134,16 +20131,16 @@
         <v>72</v>
       </c>
       <c r="B73" t="s">
+        <v>282</v>
+      </c>
+      <c r="C73" t="s">
         <v>283</v>
-      </c>
-      <c r="C73" t="s">
-        <v>284</v>
       </c>
       <c r="D73">
         <v>235361894</v>
       </c>
       <c r="E73" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F73" t="s">
         <v>81</v>
@@ -20320,7 +20317,7 @@
         <v>0</v>
       </c>
       <c r="BL73" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="BM73">
         <v>0</v>
@@ -20370,22 +20367,22 @@
         <v>73</v>
       </c>
       <c r="B74" t="s">
+        <v>282</v>
+      </c>
+      <c r="C74" t="s">
         <v>283</v>
-      </c>
-      <c r="C74" t="s">
-        <v>284</v>
       </c>
       <c r="D74">
         <v>235712152</v>
       </c>
       <c r="E74" t="s">
+        <v>291</v>
+      </c>
+      <c r="F74" t="s">
         <v>292</v>
       </c>
-      <c r="F74" t="s">
+      <c r="G74" t="s">
         <v>293</v>
-      </c>
-      <c r="G74" t="s">
-        <v>294</v>
       </c>
       <c r="H74">
         <v>8908924</v>
@@ -20606,16 +20603,16 @@
         <v>74</v>
       </c>
       <c r="B75" t="s">
+        <v>282</v>
+      </c>
+      <c r="C75" t="s">
         <v>283</v>
-      </c>
-      <c r="C75" t="s">
-        <v>284</v>
       </c>
       <c r="D75">
         <v>235375242</v>
       </c>
       <c r="E75" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="F75" t="s">
         <v>89</v>
@@ -20842,16 +20839,16 @@
         <v>75</v>
       </c>
       <c r="B76" t="s">
+        <v>282</v>
+      </c>
+      <c r="C76" t="s">
         <v>283</v>
-      </c>
-      <c r="C76" t="s">
-        <v>284</v>
       </c>
       <c r="D76">
         <v>235705915</v>
       </c>
       <c r="E76" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="F76" t="s">
         <v>89</v>
@@ -21078,22 +21075,22 @@
         <v>76</v>
       </c>
       <c r="B77" t="s">
+        <v>282</v>
+      </c>
+      <c r="C77" t="s">
         <v>283</v>
-      </c>
-      <c r="C77" t="s">
-        <v>284</v>
       </c>
       <c r="D77">
         <v>235411027</v>
       </c>
       <c r="E77" t="s">
+        <v>296</v>
+      </c>
+      <c r="F77" t="s">
         <v>297</v>
       </c>
-      <c r="F77" t="s">
+      <c r="G77" t="s">
         <v>298</v>
-      </c>
-      <c r="G77" t="s">
-        <v>299</v>
       </c>
       <c r="H77">
         <v>8908959</v>
@@ -21314,16 +21311,16 @@
         <v>77</v>
       </c>
       <c r="B78" t="s">
+        <v>282</v>
+      </c>
+      <c r="C78" t="s">
         <v>283</v>
-      </c>
-      <c r="C78" t="s">
-        <v>284</v>
       </c>
       <c r="D78">
         <v>235377377</v>
       </c>
       <c r="E78" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="F78" t="s">
         <v>89</v>
@@ -21500,7 +21497,7 @@
         <v>0</v>
       </c>
       <c r="BL78" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="BM78">
         <v>0</v>
@@ -21550,16 +21547,16 @@
         <v>78</v>
       </c>
       <c r="B79" t="s">
+        <v>301</v>
+      </c>
+      <c r="C79" t="s">
         <v>302</v>
-      </c>
-      <c r="C79" t="s">
-        <v>303</v>
       </c>
       <c r="D79">
         <v>235862219</v>
       </c>
       <c r="E79" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="F79" t="s">
         <v>106</v>
@@ -21786,16 +21783,16 @@
         <v>79</v>
       </c>
       <c r="B80" t="s">
+        <v>301</v>
+      </c>
+      <c r="C80" t="s">
         <v>302</v>
-      </c>
-      <c r="C80" t="s">
-        <v>303</v>
       </c>
       <c r="D80">
         <v>235393988</v>
       </c>
       <c r="E80" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="F80" t="s">
         <v>89</v>
@@ -22022,22 +22019,22 @@
         <v>80</v>
       </c>
       <c r="B81" t="s">
+        <v>301</v>
+      </c>
+      <c r="C81" t="s">
         <v>302</v>
-      </c>
-      <c r="C81" t="s">
-        <v>303</v>
       </c>
       <c r="D81">
         <v>235496575</v>
       </c>
       <c r="E81" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="F81" t="s">
+        <v>297</v>
+      </c>
+      <c r="G81" t="s">
         <v>298</v>
-      </c>
-      <c r="G81" t="s">
-        <v>299</v>
       </c>
       <c r="H81">
         <v>8908959</v>
@@ -22258,16 +22255,16 @@
         <v>81</v>
       </c>
       <c r="B82" t="s">
+        <v>301</v>
+      </c>
+      <c r="C82" t="s">
         <v>302</v>
-      </c>
-      <c r="C82" t="s">
-        <v>303</v>
       </c>
       <c r="D82">
         <v>235868351</v>
       </c>
       <c r="E82" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="F82" t="s">
         <v>178</v>
@@ -22494,16 +22491,16 @@
         <v>82</v>
       </c>
       <c r="B83" t="s">
+        <v>301</v>
+      </c>
+      <c r="C83" t="s">
         <v>302</v>
-      </c>
-      <c r="C83" t="s">
-        <v>303</v>
       </c>
       <c r="D83">
         <v>235366791</v>
       </c>
       <c r="E83" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="F83" t="s">
         <v>89</v>
@@ -22539,7 +22536,7 @@
         <v>1</v>
       </c>
       <c r="Q83" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="R83">
         <v>4</v>
@@ -22730,16 +22727,16 @@
         <v>83</v>
       </c>
       <c r="B84" t="s">
+        <v>301</v>
+      </c>
+      <c r="C84" t="s">
         <v>302</v>
-      </c>
-      <c r="C84" t="s">
-        <v>303</v>
       </c>
       <c r="D84">
         <v>235380939</v>
       </c>
       <c r="E84" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="F84" t="s">
         <v>138</v>
@@ -22916,7 +22913,7 @@
         <v>0</v>
       </c>
       <c r="BL84" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="BM84">
         <v>30284721</v>
@@ -22925,7 +22922,7 @@
         <v>82</v>
       </c>
       <c r="BO84" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="BP84" t="s">
         <v>82</v>
@@ -22934,7 +22931,7 @@
         <v>241</v>
       </c>
       <c r="BR84" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="BS84">
         <v>NaN</v>
@@ -22966,16 +22963,16 @@
         <v>84</v>
       </c>
       <c r="B85" t="s">
+        <v>301</v>
+      </c>
+      <c r="C85" t="s">
         <v>302</v>
-      </c>
-      <c r="C85" t="s">
-        <v>303</v>
       </c>
       <c r="D85">
         <v>235701073</v>
       </c>
       <c r="E85" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="F85" t="s">
         <v>106</v>
@@ -23202,16 +23199,16 @@
         <v>85</v>
       </c>
       <c r="B86" t="s">
+        <v>301</v>
+      </c>
+      <c r="C86" t="s">
         <v>302</v>
-      </c>
-      <c r="C86" t="s">
-        <v>303</v>
       </c>
       <c r="D86">
         <v>235397417</v>
       </c>
       <c r="E86" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="F86" t="s">
         <v>81</v>
@@ -23438,16 +23435,16 @@
         <v>86</v>
       </c>
       <c r="B87" t="s">
+        <v>301</v>
+      </c>
+      <c r="C87" t="s">
         <v>302</v>
-      </c>
-      <c r="C87" t="s">
-        <v>303</v>
       </c>
       <c r="D87">
         <v>235385792</v>
       </c>
       <c r="E87" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="F87" t="s">
         <v>89</v>
@@ -23624,7 +23621,7 @@
         <v>0</v>
       </c>
       <c r="BL87" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="BM87">
         <v>28728684</v>
@@ -23633,16 +23630,16 @@
         <v>82</v>
       </c>
       <c r="BO87" t="s">
+        <v>317</v>
+      </c>
+      <c r="BP87" t="s">
+        <v>82</v>
+      </c>
+      <c r="BQ87" t="s">
         <v>318</v>
       </c>
-      <c r="BP87" t="s">
-        <v>82</v>
-      </c>
-      <c r="BQ87" t="s">
+      <c r="BR87" t="s">
         <v>319</v>
-      </c>
-      <c r="BR87" t="s">
-        <v>320</v>
       </c>
       <c r="BS87">
         <v>NaN</v>
@@ -23674,16 +23671,16 @@
         <v>87</v>
       </c>
       <c r="B88" t="s">
+        <v>301</v>
+      </c>
+      <c r="C88" t="s">
         <v>302</v>
-      </c>
-      <c r="C88" t="s">
-        <v>303</v>
       </c>
       <c r="D88">
         <v>235366387</v>
       </c>
       <c r="E88" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="F88" t="s">
         <v>89</v>
@@ -23910,16 +23907,16 @@
         <v>88</v>
       </c>
       <c r="B89" t="s">
+        <v>321</v>
+      </c>
+      <c r="C89" t="s">
         <v>322</v>
-      </c>
-      <c r="C89" t="s">
-        <v>323</v>
       </c>
       <c r="D89">
         <v>235365256</v>
       </c>
       <c r="E89" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="F89" t="s">
         <v>119</v>
@@ -24146,16 +24143,16 @@
         <v>89</v>
       </c>
       <c r="B90" t="s">
+        <v>321</v>
+      </c>
+      <c r="C90" t="s">
         <v>322</v>
-      </c>
-      <c r="C90" t="s">
-        <v>323</v>
       </c>
       <c r="D90">
         <v>235363966</v>
       </c>
       <c r="E90" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="F90" t="s">
         <v>106</v>
@@ -24382,16 +24379,16 @@
         <v>90</v>
       </c>
       <c r="B91" t="s">
+        <v>321</v>
+      </c>
+      <c r="C91" t="s">
         <v>322</v>
-      </c>
-      <c r="C91" t="s">
-        <v>323</v>
       </c>
       <c r="D91">
         <v>235693754</v>
       </c>
       <c r="E91" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="F91" t="s">
         <v>119</v>
@@ -24538,55 +24535,55 @@
         <v>699</v>
       </c>
       <c r="BB91" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="BC91" t="s">
         <v>122</v>
       </c>
       <c r="BD91" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="BE91" t="s">
         <v>122</v>
       </c>
       <c r="BF91" t="s">
+        <v>328</v>
+      </c>
+      <c r="BG91" t="s">
+        <v>82</v>
+      </c>
+      <c r="BH91">
+        <v>0</v>
+      </c>
+      <c r="BI91" t="s">
+        <v>82</v>
+      </c>
+      <c r="BJ91" t="s">
         <v>329</v>
-      </c>
-      <c r="BG91" t="s">
-        <v>82</v>
-      </c>
-      <c r="BH91">
-        <v>0</v>
-      </c>
-      <c r="BI91" t="s">
-        <v>82</v>
-      </c>
-      <c r="BJ91" t="s">
-        <v>330</v>
       </c>
       <c r="BK91">
         <v>8887810</v>
       </c>
       <c r="BL91" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="BM91">
         <v>4372840</v>
       </c>
       <c r="BN91" t="s">
+        <v>331</v>
+      </c>
+      <c r="BO91" t="s">
         <v>332</v>
-      </c>
-      <c r="BO91" t="s">
-        <v>333</v>
       </c>
       <c r="BP91" t="s">
         <v>228</v>
       </c>
       <c r="BQ91" t="s">
+        <v>333</v>
+      </c>
+      <c r="BR91" t="s">
         <v>334</v>
-      </c>
-      <c r="BR91" t="s">
-        <v>335</v>
       </c>
       <c r="BS91">
         <v>NaN</v>
@@ -24595,7 +24592,7 @@
         <v>82</v>
       </c>
       <c r="BU91" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="BV91">
         <v>3194</v>
@@ -24618,16 +24615,16 @@
         <v>91</v>
       </c>
       <c r="B92" t="s">
+        <v>321</v>
+      </c>
+      <c r="C92" t="s">
         <v>322</v>
-      </c>
-      <c r="C92" t="s">
-        <v>323</v>
       </c>
       <c r="D92">
         <v>235484251</v>
       </c>
       <c r="E92" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="F92" t="s">
         <v>89</v>
@@ -24854,16 +24851,16 @@
         <v>92</v>
       </c>
       <c r="B93" t="s">
+        <v>321</v>
+      </c>
+      <c r="C93" t="s">
         <v>322</v>
-      </c>
-      <c r="C93" t="s">
-        <v>323</v>
       </c>
       <c r="D93">
         <v>235362382</v>
       </c>
       <c r="E93" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="F93" t="s">
         <v>89</v>
@@ -25090,16 +25087,16 @@
         <v>93</v>
       </c>
       <c r="B94" t="s">
+        <v>321</v>
+      </c>
+      <c r="C94" t="s">
         <v>322</v>
-      </c>
-      <c r="C94" t="s">
-        <v>323</v>
       </c>
       <c r="D94">
         <v>235401872</v>
       </c>
       <c r="E94" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="F94" t="s">
         <v>89</v>
@@ -25276,7 +25273,7 @@
         <v>0</v>
       </c>
       <c r="BL94" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="BM94">
         <v>231986857</v>
@@ -25285,16 +25282,16 @@
         <v>82</v>
       </c>
       <c r="BO94" t="s">
+        <v>340</v>
+      </c>
+      <c r="BP94" t="s">
+        <v>82</v>
+      </c>
+      <c r="BQ94" t="s">
         <v>341</v>
       </c>
-      <c r="BP94" t="s">
-        <v>82</v>
-      </c>
-      <c r="BQ94" t="s">
+      <c r="BR94" t="s">
         <v>342</v>
-      </c>
-      <c r="BR94" t="s">
-        <v>343</v>
       </c>
       <c r="BS94">
         <v>NaN</v>
@@ -25326,16 +25323,16 @@
         <v>94</v>
       </c>
       <c r="B95" t="s">
+        <v>321</v>
+      </c>
+      <c r="C95" t="s">
         <v>322</v>
-      </c>
-      <c r="C95" t="s">
-        <v>323</v>
       </c>
       <c r="D95">
         <v>235363968</v>
       </c>
       <c r="E95" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="F95" t="s">
         <v>89</v>
@@ -25562,16 +25559,16 @@
         <v>95</v>
       </c>
       <c r="B96" t="s">
+        <v>321</v>
+      </c>
+      <c r="C96" t="s">
         <v>322</v>
-      </c>
-      <c r="C96" t="s">
-        <v>323</v>
       </c>
       <c r="D96">
         <v>235363352</v>
       </c>
       <c r="E96" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="F96" t="s">
         <v>106</v>
@@ -25798,16 +25795,16 @@
         <v>96</v>
       </c>
       <c r="B97" t="s">
+        <v>321</v>
+      </c>
+      <c r="C97" t="s">
         <v>322</v>
-      </c>
-      <c r="C97" t="s">
-        <v>323</v>
       </c>
       <c r="D97">
         <v>235468625</v>
       </c>
       <c r="E97" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="F97" t="s">
         <v>138</v>
@@ -26034,16 +26031,16 @@
         <v>97</v>
       </c>
       <c r="B98" t="s">
+        <v>321</v>
+      </c>
+      <c r="C98" t="s">
         <v>322</v>
-      </c>
-      <c r="C98" t="s">
-        <v>323</v>
       </c>
       <c r="D98">
         <v>235710931</v>
       </c>
       <c r="E98" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="F98" t="s">
         <v>89</v>
@@ -26270,16 +26267,16 @@
         <v>98</v>
       </c>
       <c r="B99" t="s">
+        <v>347</v>
+      </c>
+      <c r="C99" t="s">
         <v>348</v>
-      </c>
-      <c r="C99" t="s">
-        <v>349</v>
       </c>
       <c r="D99">
         <v>235697014</v>
       </c>
       <c r="E99" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="F99" t="s">
         <v>89</v>
@@ -26506,16 +26503,16 @@
         <v>99</v>
       </c>
       <c r="B100" t="s">
+        <v>347</v>
+      </c>
+      <c r="C100" t="s">
         <v>348</v>
-      </c>
-      <c r="C100" t="s">
-        <v>349</v>
       </c>
       <c r="D100">
         <v>235364209</v>
       </c>
       <c r="E100" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="F100" t="s">
         <v>89</v>
@@ -26742,16 +26739,16 @@
         <v>100</v>
       </c>
       <c r="B101" t="s">
+        <v>347</v>
+      </c>
+      <c r="C101" t="s">
         <v>348</v>
-      </c>
-      <c r="C101" t="s">
-        <v>349</v>
       </c>
       <c r="D101">
         <v>235379682</v>
       </c>
       <c r="E101" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="F101" t="s">
         <v>138</v>
@@ -26928,7 +26925,7 @@
         <v>0</v>
       </c>
       <c r="BL101" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="BM101">
         <v>263054156</v>
@@ -26937,16 +26934,16 @@
         <v>82</v>
       </c>
       <c r="BO101" t="s">
+        <v>353</v>
+      </c>
+      <c r="BP101" t="s">
+        <v>82</v>
+      </c>
+      <c r="BQ101" t="s">
         <v>354</v>
       </c>
-      <c r="BP101" t="s">
-        <v>82</v>
-      </c>
-      <c r="BQ101" t="s">
+      <c r="BR101" t="s">
         <v>355</v>
-      </c>
-      <c r="BR101" t="s">
-        <v>356</v>
       </c>
       <c r="BS101">
         <v>NaN</v>
@@ -26978,16 +26975,16 @@
         <v>101</v>
       </c>
       <c r="B102" t="s">
+        <v>347</v>
+      </c>
+      <c r="C102" t="s">
         <v>348</v>
-      </c>
-      <c r="C102" t="s">
-        <v>349</v>
       </c>
       <c r="D102">
         <v>235389470</v>
       </c>
       <c r="E102" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="F102" t="s">
         <v>106</v>
@@ -27214,16 +27211,16 @@
         <v>102</v>
       </c>
       <c r="B103" t="s">
+        <v>347</v>
+      </c>
+      <c r="C103" t="s">
         <v>348</v>
-      </c>
-      <c r="C103" t="s">
-        <v>349</v>
       </c>
       <c r="D103">
         <v>235414951</v>
       </c>
       <c r="E103" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="F103" t="s">
         <v>138</v>
@@ -27450,16 +27447,16 @@
         <v>103</v>
       </c>
       <c r="B104" t="s">
+        <v>347</v>
+      </c>
+      <c r="C104" t="s">
         <v>348</v>
-      </c>
-      <c r="C104" t="s">
-        <v>349</v>
       </c>
       <c r="D104">
         <v>235736407</v>
       </c>
       <c r="E104" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="F104" t="s">
         <v>89</v>
@@ -27686,16 +27683,16 @@
         <v>104</v>
       </c>
       <c r="B105" t="s">
+        <v>347</v>
+      </c>
+      <c r="C105" t="s">
         <v>348</v>
-      </c>
-      <c r="C105" t="s">
-        <v>349</v>
       </c>
       <c r="D105">
         <v>235693297</v>
       </c>
       <c r="E105" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="F105" t="s">
         <v>138</v>
@@ -27922,16 +27919,16 @@
         <v>105</v>
       </c>
       <c r="B106" t="s">
+        <v>347</v>
+      </c>
+      <c r="C106" t="s">
         <v>348</v>
-      </c>
-      <c r="C106" t="s">
-        <v>349</v>
       </c>
       <c r="D106">
         <v>235692699</v>
       </c>
       <c r="E106" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="F106" t="s">
         <v>163</v>
@@ -28158,16 +28155,16 @@
         <v>106</v>
       </c>
       <c r="B107" t="s">
+        <v>347</v>
+      </c>
+      <c r="C107" t="s">
         <v>348</v>
-      </c>
-      <c r="C107" t="s">
-        <v>349</v>
       </c>
       <c r="D107">
         <v>235362852</v>
       </c>
       <c r="E107" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="F107" t="s">
         <v>138</v>
@@ -28344,7 +28341,7 @@
         <v>0</v>
       </c>
       <c r="BL107" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="BM107">
         <v>0</v>
@@ -28394,16 +28391,16 @@
         <v>107</v>
       </c>
       <c r="B108" t="s">
+        <v>347</v>
+      </c>
+      <c r="C108" t="s">
         <v>348</v>
-      </c>
-      <c r="C108" t="s">
-        <v>349</v>
       </c>
       <c r="D108">
         <v>235368876</v>
       </c>
       <c r="E108" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="F108" t="s">
         <v>106</v>
@@ -28439,7 +28436,7 @@
         <v>4</v>
       </c>
       <c r="Q108" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="R108">
         <v>4</v>
@@ -28580,7 +28577,7 @@
         <v>0</v>
       </c>
       <c r="BL108" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="BM108">
         <v>0</v>
@@ -28639,7 +28636,7 @@
         <v>235364558</v>
       </c>
       <c r="E109" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="F109" t="s">
         <v>89</v>
@@ -28875,7 +28872,7 @@
         <v>235363039</v>
       </c>
       <c r="E110" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="F110" t="s">
         <v>89</v>
@@ -29111,7 +29108,7 @@
         <v>235403163</v>
       </c>
       <c r="E111" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="F111" t="s">
         <v>138</v>
@@ -29288,7 +29285,7 @@
         <v>0</v>
       </c>
       <c r="BL111" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="BM111">
         <v>226533760</v>
@@ -29297,16 +29294,16 @@
         <v>82</v>
       </c>
       <c r="BO111" t="s">
+        <v>369</v>
+      </c>
+      <c r="BP111" t="s">
+        <v>82</v>
+      </c>
+      <c r="BQ111" t="s">
         <v>370</v>
       </c>
-      <c r="BP111" t="s">
-        <v>82</v>
-      </c>
-      <c r="BQ111" t="s">
+      <c r="BR111" t="s">
         <v>371</v>
-      </c>
-      <c r="BR111" t="s">
-        <v>372</v>
       </c>
       <c r="BS111">
         <v>NaN</v>
@@ -29347,7 +29344,7 @@
         <v>235399849</v>
       </c>
       <c r="E112" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="F112" t="s">
         <v>138</v>
@@ -29583,7 +29580,7 @@
         <v>235695978</v>
       </c>
       <c r="E113" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="F113" t="s">
         <v>89</v>
@@ -29819,7 +29816,7 @@
         <v>235722229</v>
       </c>
       <c r="E114" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="F114" t="s">
         <v>89</v>
@@ -30055,7 +30052,7 @@
         <v>235363752</v>
       </c>
       <c r="E115" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="F115" t="s">
         <v>89</v>
@@ -30291,7 +30288,7 @@
         <v>235403972</v>
       </c>
       <c r="E116" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="F116" t="s">
         <v>178</v>
@@ -30527,7 +30524,7 @@
         <v>235382565</v>
       </c>
       <c r="E117" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="F117" t="s">
         <v>106</v>
@@ -30563,7 +30560,7 @@
         <v>5</v>
       </c>
       <c r="Q117" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="R117">
         <v>12</v>
@@ -30763,7 +30760,7 @@
         <v>235363060</v>
       </c>
       <c r="E118" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="F118" t="s">
         <v>81</v>
@@ -30999,7 +30996,7 @@
         <v>235364134</v>
       </c>
       <c r="E119" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="F119" t="s">
         <v>178</v>
@@ -31235,7 +31232,7 @@
         <v>235732766</v>
       </c>
       <c r="E120" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="F120" t="s">
         <v>94</v>
@@ -31471,7 +31468,7 @@
         <v>235362707</v>
       </c>
       <c r="E121" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="F121" t="s">
         <v>106</v>
@@ -31707,13 +31704,13 @@
         <v>235744992</v>
       </c>
       <c r="E122" t="s">
+        <v>383</v>
+      </c>
+      <c r="F122" t="s">
         <v>384</v>
       </c>
-      <c r="F122" t="s">
+      <c r="G122" t="s">
         <v>385</v>
-      </c>
-      <c r="G122" t="s">
-        <v>386</v>
       </c>
       <c r="H122">
         <v>8909361</v>
@@ -31943,7 +31940,7 @@
         <v>235513968</v>
       </c>
       <c r="E123" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="F123" t="s">
         <v>106</v>
@@ -32120,7 +32117,7 @@
         <v>0</v>
       </c>
       <c r="BL123" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="BM123">
         <v>0</v>
@@ -32170,22 +32167,22 @@
         <v>123</v>
       </c>
       <c r="B124" t="s">
+        <v>388</v>
+      </c>
+      <c r="C124" t="s">
         <v>389</v>
-      </c>
-      <c r="C124" t="s">
-        <v>390</v>
       </c>
       <c r="D124">
         <v>235720859</v>
       </c>
       <c r="E124" t="s">
+        <v>390</v>
+      </c>
+      <c r="F124" t="s">
         <v>391</v>
       </c>
-      <c r="F124" t="s">
+      <c r="G124" t="s">
         <v>392</v>
-      </c>
-      <c r="G124" t="s">
-        <v>393</v>
       </c>
       <c r="H124">
         <v>8909536</v>
@@ -32415,7 +32412,7 @@
         <v>235505236</v>
       </c>
       <c r="E125" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="F125" t="s">
         <v>89</v>
@@ -32642,16 +32639,16 @@
         <v>125</v>
       </c>
       <c r="B126" t="s">
+        <v>394</v>
+      </c>
+      <c r="C126" t="s">
         <v>395</v>
-      </c>
-      <c r="C126" t="s">
-        <v>396</v>
       </c>
       <c r="D126">
         <v>235422854</v>
       </c>
       <c r="E126" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="F126" t="s">
         <v>178</v>
@@ -32878,16 +32875,16 @@
         <v>126</v>
       </c>
       <c r="B127" t="s">
+        <v>394</v>
+      </c>
+      <c r="C127" t="s">
         <v>395</v>
-      </c>
-      <c r="C127" t="s">
-        <v>396</v>
       </c>
       <c r="D127">
         <v>235822906</v>
       </c>
       <c r="E127" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="F127" t="s">
         <v>178</v>
@@ -33114,16 +33111,16 @@
         <v>127</v>
       </c>
       <c r="B128" t="s">
+        <v>394</v>
+      </c>
+      <c r="C128" t="s">
         <v>395</v>
-      </c>
-      <c r="C128" t="s">
-        <v>396</v>
       </c>
       <c r="D128">
         <v>235497701</v>
       </c>
       <c r="E128" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="F128" t="s">
         <v>89</v>
@@ -33350,16 +33347,16 @@
         <v>128</v>
       </c>
       <c r="B129" t="s">
+        <v>394</v>
+      </c>
+      <c r="C129" t="s">
         <v>395</v>
-      </c>
-      <c r="C129" t="s">
-        <v>396</v>
       </c>
       <c r="D129">
         <v>235427514</v>
       </c>
       <c r="E129" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="F129" t="s">
         <v>138</v>
@@ -33586,16 +33583,16 @@
         <v>129</v>
       </c>
       <c r="B130" t="s">
+        <v>394</v>
+      </c>
+      <c r="C130" t="s">
         <v>395</v>
-      </c>
-      <c r="C130" t="s">
-        <v>396</v>
       </c>
       <c r="D130">
         <v>235537345</v>
       </c>
       <c r="E130" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="F130" t="s">
         <v>106</v>
@@ -33822,16 +33819,16 @@
         <v>130</v>
       </c>
       <c r="B131" t="s">
+        <v>394</v>
+      </c>
+      <c r="C131" t="s">
         <v>395</v>
-      </c>
-      <c r="C131" t="s">
-        <v>396</v>
       </c>
       <c r="D131">
         <v>235367808</v>
       </c>
       <c r="E131" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="F131" t="s">
         <v>138</v>
@@ -34058,16 +34055,16 @@
         <v>131</v>
       </c>
       <c r="B132" t="s">
+        <v>394</v>
+      </c>
+      <c r="C132" t="s">
         <v>395</v>
-      </c>
-      <c r="C132" t="s">
-        <v>396</v>
       </c>
       <c r="D132">
         <v>235410815</v>
       </c>
       <c r="E132" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="F132" t="s">
         <v>138</v>
@@ -34294,16 +34291,16 @@
         <v>132</v>
       </c>
       <c r="B133" t="s">
+        <v>394</v>
+      </c>
+      <c r="C133" t="s">
         <v>395</v>
-      </c>
-      <c r="C133" t="s">
-        <v>396</v>
       </c>
       <c r="D133">
         <v>235707573</v>
       </c>
       <c r="E133" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="F133" t="s">
         <v>89</v>
@@ -34530,16 +34527,16 @@
         <v>133</v>
       </c>
       <c r="B134" t="s">
+        <v>394</v>
+      </c>
+      <c r="C134" t="s">
         <v>395</v>
-      </c>
-      <c r="C134" t="s">
-        <v>396</v>
       </c>
       <c r="D134">
         <v>235805287</v>
       </c>
       <c r="E134" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="F134" t="s">
         <v>178</v>
@@ -34766,16 +34763,16 @@
         <v>134</v>
       </c>
       <c r="B135" t="s">
+        <v>394</v>
+      </c>
+      <c r="C135" t="s">
         <v>395</v>
-      </c>
-      <c r="C135" t="s">
-        <v>396</v>
       </c>
       <c r="D135">
         <v>235438961</v>
       </c>
       <c r="E135" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="F135" t="s">
         <v>169</v>
@@ -35002,16 +34999,16 @@
         <v>135</v>
       </c>
       <c r="B136" t="s">
+        <v>406</v>
+      </c>
+      <c r="C136" t="s">
         <v>407</v>
-      </c>
-      <c r="C136" t="s">
-        <v>408</v>
       </c>
       <c r="D136">
         <v>235447965</v>
       </c>
       <c r="E136" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="F136" t="s">
         <v>178</v>
@@ -35238,16 +35235,16 @@
         <v>136</v>
       </c>
       <c r="B137" t="s">
+        <v>406</v>
+      </c>
+      <c r="C137" t="s">
         <v>407</v>
-      </c>
-      <c r="C137" t="s">
-        <v>408</v>
       </c>
       <c r="D137">
         <v>235693449</v>
       </c>
       <c r="E137" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="F137" t="s">
         <v>89</v>
@@ -35283,7 +35280,7 @@
         <v>5</v>
       </c>
       <c r="Q137" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="R137">
         <v>10</v>
@@ -35474,16 +35471,16 @@
         <v>137</v>
       </c>
       <c r="B138" t="s">
+        <v>406</v>
+      </c>
+      <c r="C138" t="s">
         <v>407</v>
-      </c>
-      <c r="C138" t="s">
-        <v>408</v>
       </c>
       <c r="D138">
         <v>235752638</v>
       </c>
       <c r="E138" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="F138" t="s">
         <v>89</v>
@@ -35660,7 +35657,7 @@
         <v>0</v>
       </c>
       <c r="BL138" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="BM138">
         <v>24336001</v>
@@ -35669,16 +35666,16 @@
         <v>82</v>
       </c>
       <c r="BO138" t="s">
+        <v>413</v>
+      </c>
+      <c r="BP138" t="s">
+        <v>82</v>
+      </c>
+      <c r="BQ138" t="s">
+        <v>333</v>
+      </c>
+      <c r="BR138" t="s">
         <v>414</v>
-      </c>
-      <c r="BP138" t="s">
-        <v>82</v>
-      </c>
-      <c r="BQ138" t="s">
-        <v>334</v>
-      </c>
-      <c r="BR138" t="s">
-        <v>415</v>
       </c>
       <c r="BS138">
         <v>NaN</v>
@@ -35710,22 +35707,22 @@
         <v>138</v>
       </c>
       <c r="B139" t="s">
+        <v>406</v>
+      </c>
+      <c r="C139" t="s">
         <v>407</v>
-      </c>
-      <c r="C139" t="s">
-        <v>408</v>
       </c>
       <c r="D139">
         <v>235429970</v>
       </c>
       <c r="E139" t="s">
+        <v>415</v>
+      </c>
+      <c r="F139" t="s">
         <v>416</v>
       </c>
-      <c r="F139" t="s">
+      <c r="G139" t="s">
         <v>417</v>
-      </c>
-      <c r="G139" t="s">
-        <v>418</v>
       </c>
       <c r="H139">
         <v>8930765</v>
@@ -35896,7 +35893,7 @@
         <v>0</v>
       </c>
       <c r="BL139" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="BM139">
         <v>28755052</v>
@@ -35905,7 +35902,7 @@
         <v>82</v>
       </c>
       <c r="BO139" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="BP139" t="s">
         <v>82</v>
@@ -35914,7 +35911,7 @@
         <v>175</v>
       </c>
       <c r="BR139" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="BS139">
         <v>NaN</v>
@@ -35946,16 +35943,16 @@
         <v>139</v>
       </c>
       <c r="B140" t="s">
+        <v>406</v>
+      </c>
+      <c r="C140" t="s">
         <v>407</v>
-      </c>
-      <c r="C140" t="s">
-        <v>408</v>
       </c>
       <c r="D140">
         <v>235364966</v>
       </c>
       <c r="E140" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="F140" t="s">
         <v>138</v>
@@ -35991,7 +35988,7 @@
         <v>2</v>
       </c>
       <c r="Q140" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="R140">
         <v>4</v>
@@ -36132,7 +36129,7 @@
         <v>0</v>
       </c>
       <c r="BL140" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="BM140">
         <v>246905407</v>
@@ -36141,16 +36138,16 @@
         <v>82</v>
       </c>
       <c r="BO140" t="s">
+        <v>423</v>
+      </c>
+      <c r="BP140" t="s">
+        <v>82</v>
+      </c>
+      <c r="BQ140" t="s">
         <v>424</v>
       </c>
-      <c r="BP140" t="s">
-        <v>82</v>
-      </c>
-      <c r="BQ140" t="s">
+      <c r="BR140" t="s">
         <v>425</v>
-      </c>
-      <c r="BR140" t="s">
-        <v>426</v>
       </c>
       <c r="BS140">
         <v>NaN</v>
@@ -36182,16 +36179,16 @@
         <v>140</v>
       </c>
       <c r="B141" t="s">
+        <v>406</v>
+      </c>
+      <c r="C141" t="s">
         <v>407</v>
-      </c>
-      <c r="C141" t="s">
-        <v>408</v>
       </c>
       <c r="D141">
         <v>235386136</v>
       </c>
       <c r="E141" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="F141" t="s">
         <v>178</v>
@@ -36418,16 +36415,16 @@
         <v>141</v>
       </c>
       <c r="B142" t="s">
+        <v>406</v>
+      </c>
+      <c r="C142" t="s">
         <v>407</v>
-      </c>
-      <c r="C142" t="s">
-        <v>408</v>
       </c>
       <c r="D142">
         <v>235365974</v>
       </c>
       <c r="E142" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="F142" t="s">
         <v>106</v>
@@ -36604,7 +36601,7 @@
         <v>0</v>
       </c>
       <c r="BL142" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="BM142">
         <v>0</v>
@@ -36654,16 +36651,16 @@
         <v>142</v>
       </c>
       <c r="B143" t="s">
+        <v>406</v>
+      </c>
+      <c r="C143" t="s">
         <v>407</v>
-      </c>
-      <c r="C143" t="s">
-        <v>408</v>
       </c>
       <c r="D143">
         <v>235367003</v>
       </c>
       <c r="E143" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="F143" t="s">
         <v>169</v>
@@ -36890,16 +36887,16 @@
         <v>143</v>
       </c>
       <c r="B144" t="s">
+        <v>406</v>
+      </c>
+      <c r="C144" t="s">
         <v>407</v>
-      </c>
-      <c r="C144" t="s">
-        <v>408</v>
       </c>
       <c r="D144">
         <v>235455266</v>
       </c>
       <c r="E144" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="F144" t="s">
         <v>106</v>
@@ -37126,16 +37123,16 @@
         <v>144</v>
       </c>
       <c r="B145" t="s">
+        <v>406</v>
+      </c>
+      <c r="C145" t="s">
         <v>407</v>
-      </c>
-      <c r="C145" t="s">
-        <v>408</v>
       </c>
       <c r="D145">
         <v>235367241</v>
       </c>
       <c r="E145" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="F145" t="s">
         <v>138</v>
@@ -37312,7 +37309,7 @@
         <v>0</v>
       </c>
       <c r="BL145" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="BM145">
         <v>0</v>
@@ -37362,16 +37359,16 @@
         <v>145</v>
       </c>
       <c r="B146" t="s">
+        <v>406</v>
+      </c>
+      <c r="C146" t="s">
         <v>407</v>
-      </c>
-      <c r="C146" t="s">
-        <v>408</v>
       </c>
       <c r="D146">
         <v>235368264</v>
       </c>
       <c r="E146" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="F146" t="s">
         <v>106</v>
@@ -37598,16 +37595,16 @@
         <v>146</v>
       </c>
       <c r="B147" t="s">
+        <v>434</v>
+      </c>
+      <c r="C147" t="s">
         <v>435</v>
-      </c>
-      <c r="C147" t="s">
-        <v>436</v>
       </c>
       <c r="D147">
         <v>235380427</v>
       </c>
       <c r="E147" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="F147" t="s">
         <v>106</v>
@@ -37834,16 +37831,16 @@
         <v>147</v>
       </c>
       <c r="B148" t="s">
+        <v>437</v>
+      </c>
+      <c r="C148" t="s">
         <v>438</v>
-      </c>
-      <c r="C148" t="s">
-        <v>439</v>
       </c>
       <c r="D148">
         <v>235398207</v>
       </c>
       <c r="E148" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="F148" t="s">
         <v>106</v>
@@ -38070,16 +38067,16 @@
         <v>148</v>
       </c>
       <c r="B149" t="s">
+        <v>437</v>
+      </c>
+      <c r="C149" t="s">
         <v>438</v>
-      </c>
-      <c r="C149" t="s">
-        <v>439</v>
       </c>
       <c r="D149">
         <v>235774594</v>
       </c>
       <c r="E149" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="F149" t="s">
         <v>138</v>
@@ -38256,7 +38253,7 @@
         <v>0</v>
       </c>
       <c r="BL149" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="BM149">
         <v>0</v>
@@ -38306,16 +38303,16 @@
         <v>149</v>
       </c>
       <c r="B150" t="s">
+        <v>437</v>
+      </c>
+      <c r="C150" t="s">
         <v>438</v>
-      </c>
-      <c r="C150" t="s">
-        <v>439</v>
       </c>
       <c r="D150">
         <v>235365947</v>
       </c>
       <c r="E150" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="F150" t="s">
         <v>106</v>
@@ -38542,16 +38539,16 @@
         <v>150</v>
       </c>
       <c r="B151" t="s">
+        <v>434</v>
+      </c>
+      <c r="C151" t="s">
         <v>435</v>
-      </c>
-      <c r="C151" t="s">
-        <v>436</v>
       </c>
       <c r="D151">
         <v>235422534</v>
       </c>
       <c r="E151" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="F151" t="s">
         <v>178</v>
@@ -38778,16 +38775,16 @@
         <v>151</v>
       </c>
       <c r="B152" t="s">
+        <v>437</v>
+      </c>
+      <c r="C152" t="s">
         <v>438</v>
-      </c>
-      <c r="C152" t="s">
-        <v>439</v>
       </c>
       <c r="D152">
         <v>235693223</v>
       </c>
       <c r="E152" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="F152" t="s">
         <v>106</v>
@@ -39014,16 +39011,16 @@
         <v>152</v>
       </c>
       <c r="B153" t="s">
+        <v>437</v>
+      </c>
+      <c r="C153" t="s">
         <v>438</v>
-      </c>
-      <c r="C153" t="s">
-        <v>439</v>
       </c>
       <c r="D153">
         <v>235694555</v>
       </c>
       <c r="E153" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="F153" t="s">
         <v>106</v>
@@ -39250,16 +39247,16 @@
         <v>153</v>
       </c>
       <c r="B154" t="s">
+        <v>437</v>
+      </c>
+      <c r="C154" t="s">
         <v>438</v>
-      </c>
-      <c r="C154" t="s">
-        <v>439</v>
       </c>
       <c r="D154">
         <v>235383433</v>
       </c>
       <c r="E154" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="F154" t="s">
         <v>89</v>
@@ -39436,7 +39433,7 @@
         <v>0</v>
       </c>
       <c r="BL154" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="BM154">
         <v>263037583</v>
@@ -39445,16 +39442,16 @@
         <v>82</v>
       </c>
       <c r="BO154" t="s">
+        <v>448</v>
+      </c>
+      <c r="BP154" t="s">
+        <v>82</v>
+      </c>
+      <c r="BQ154" t="s">
         <v>449</v>
       </c>
-      <c r="BP154" t="s">
-        <v>82</v>
-      </c>
-      <c r="BQ154" t="s">
+      <c r="BR154" t="s">
         <v>450</v>
-      </c>
-      <c r="BR154" t="s">
-        <v>451</v>
       </c>
       <c r="BS154">
         <v>NaN</v>
@@ -39486,16 +39483,16 @@
         <v>154</v>
       </c>
       <c r="B155" t="s">
+        <v>437</v>
+      </c>
+      <c r="C155" t="s">
         <v>438</v>
-      </c>
-      <c r="C155" t="s">
-        <v>439</v>
       </c>
       <c r="D155">
         <v>235421473</v>
       </c>
       <c r="E155" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="F155" t="s">
         <v>94</v>
@@ -39672,7 +39669,7 @@
         <v>0</v>
       </c>
       <c r="BL155" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="BM155">
         <v>0</v>
@@ -39722,16 +39719,16 @@
         <v>155</v>
       </c>
       <c r="B156" t="s">
+        <v>437</v>
+      </c>
+      <c r="C156" t="s">
         <v>438</v>
-      </c>
-      <c r="C156" t="s">
-        <v>439</v>
       </c>
       <c r="D156">
         <v>235426751</v>
       </c>
       <c r="E156" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="F156" t="s">
         <v>138</v>
@@ -39917,16 +39914,16 @@
         <v>82</v>
       </c>
       <c r="BO156" t="s">
+        <v>454</v>
+      </c>
+      <c r="BP156" t="s">
+        <v>82</v>
+      </c>
+      <c r="BQ156" t="s">
+        <v>341</v>
+      </c>
+      <c r="BR156" t="s">
         <v>455</v>
-      </c>
-      <c r="BP156" t="s">
-        <v>82</v>
-      </c>
-      <c r="BQ156" t="s">
-        <v>342</v>
-      </c>
-      <c r="BR156" t="s">
-        <v>456</v>
       </c>
       <c r="BS156">
         <v>NaN</v>
@@ -39958,16 +39955,16 @@
         <v>156</v>
       </c>
       <c r="B157" t="s">
+        <v>437</v>
+      </c>
+      <c r="C157" t="s">
         <v>438</v>
-      </c>
-      <c r="C157" t="s">
-        <v>439</v>
       </c>
       <c r="D157">
         <v>235391795</v>
       </c>
       <c r="E157" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="F157" t="s">
         <v>106</v>
@@ -40144,7 +40141,7 @@
         <v>0</v>
       </c>
       <c r="BL157" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="BM157">
         <v>262661768</v>
@@ -40153,7 +40150,7 @@
         <v>82</v>
       </c>
       <c r="BO157" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="BP157" t="s">
         <v>82</v>
@@ -40162,7 +40159,7 @@
         <v>188</v>
       </c>
       <c r="BR157" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="BS157">
         <v>NaN</v>
@@ -40194,16 +40191,16 @@
         <v>157</v>
       </c>
       <c r="B158" t="s">
+        <v>434</v>
+      </c>
+      <c r="C158" t="s">
         <v>435</v>
-      </c>
-      <c r="C158" t="s">
-        <v>436</v>
       </c>
       <c r="D158">
         <v>235365693</v>
       </c>
       <c r="E158" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="F158" t="s">
         <v>138</v>
@@ -40239,7 +40236,7 @@
         <v>2</v>
       </c>
       <c r="Q158" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="R158">
         <v>4</v>
@@ -40389,7 +40386,7 @@
         <v>82</v>
       </c>
       <c r="BO158" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="BP158" t="s">
         <v>82</v>
@@ -40398,7 +40395,7 @@
         <v>188</v>
       </c>
       <c r="BR158" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="BS158">
         <v>NaN</v>
@@ -40430,16 +40427,16 @@
         <v>158</v>
       </c>
       <c r="B159" t="s">
+        <v>437</v>
+      </c>
+      <c r="C159" t="s">
         <v>438</v>
-      </c>
-      <c r="C159" t="s">
-        <v>439</v>
       </c>
       <c r="D159">
         <v>235692860</v>
       </c>
       <c r="E159" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="F159" t="s">
         <v>89</v>
@@ -40616,7 +40613,7 @@
         <v>0</v>
       </c>
       <c r="BL159" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="BM159">
         <v>30605510</v>
@@ -40625,7 +40622,7 @@
         <v>82</v>
       </c>
       <c r="BO159" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="BP159" t="s">
         <v>82</v>
@@ -40634,7 +40631,7 @@
         <v>229</v>
       </c>
       <c r="BR159" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="BS159">
         <v>NaN</v>
@@ -40666,16 +40663,16 @@
         <v>159</v>
       </c>
       <c r="B160" t="s">
+        <v>467</v>
+      </c>
+      <c r="C160" t="s">
         <v>468</v>
-      </c>
-      <c r="C160" t="s">
-        <v>469</v>
       </c>
       <c r="D160">
         <v>235393400</v>
       </c>
       <c r="E160" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="F160" t="s">
         <v>89</v>
@@ -40852,7 +40849,7 @@
         <v>0</v>
       </c>
       <c r="BL160" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="BM160">
         <v>28035025</v>
@@ -40861,16 +40858,16 @@
         <v>82</v>
       </c>
       <c r="BO160" t="s">
+        <v>471</v>
+      </c>
+      <c r="BP160" t="s">
+        <v>82</v>
+      </c>
+      <c r="BQ160" t="s">
+        <v>341</v>
+      </c>
+      <c r="BR160" t="s">
         <v>472</v>
-      </c>
-      <c r="BP160" t="s">
-        <v>82</v>
-      </c>
-      <c r="BQ160" t="s">
-        <v>342</v>
-      </c>
-      <c r="BR160" t="s">
-        <v>473</v>
       </c>
       <c r="BS160">
         <v>NaN</v>
@@ -40902,16 +40899,16 @@
         <v>160</v>
       </c>
       <c r="B161" t="s">
+        <v>434</v>
+      </c>
+      <c r="C161" t="s">
         <v>435</v>
-      </c>
-      <c r="C161" t="s">
-        <v>436</v>
       </c>
       <c r="D161">
         <v>235367608</v>
       </c>
       <c r="E161" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="F161" t="s">
         <v>89</v>
@@ -41088,7 +41085,7 @@
         <v>0</v>
       </c>
       <c r="BL161" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="BM161">
         <v>263051736</v>
@@ -41097,22 +41094,22 @@
         <v>82</v>
       </c>
       <c r="BO161" t="s">
+        <v>475</v>
+      </c>
+      <c r="BP161" t="s">
+        <v>82</v>
+      </c>
+      <c r="BQ161" t="s">
         <v>476</v>
       </c>
-      <c r="BP161" t="s">
-        <v>82</v>
-      </c>
-      <c r="BQ161" t="s">
+      <c r="BR161" t="s">
         <v>477</v>
-      </c>
-      <c r="BR161" t="s">
-        <v>478</v>
       </c>
       <c r="BS161">
         <v>NaN</v>
       </c>
       <c r="BT161" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="BU161" t="s">
         <v>82</v>
@@ -41138,16 +41135,16 @@
         <v>161</v>
       </c>
       <c r="B162" t="s">
+        <v>467</v>
+      </c>
+      <c r="C162" t="s">
         <v>468</v>
-      </c>
-      <c r="C162" t="s">
-        <v>469</v>
       </c>
       <c r="D162">
         <v>235481439</v>
       </c>
       <c r="E162" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="F162" t="s">
         <v>106</v>
@@ -41324,7 +41321,7 @@
         <v>0</v>
       </c>
       <c r="BL162" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="BM162">
         <v>28764761</v>
@@ -41333,7 +41330,7 @@
         <v>82</v>
       </c>
       <c r="BO162" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="BP162" t="s">
         <v>82</v>
@@ -41342,7 +41339,7 @@
         <v>130</v>
       </c>
       <c r="BR162" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="BS162">
         <v>NaN</v>
@@ -41374,16 +41371,16 @@
         <v>162</v>
       </c>
       <c r="B163" t="s">
+        <v>467</v>
+      </c>
+      <c r="C163" t="s">
         <v>468</v>
-      </c>
-      <c r="C163" t="s">
-        <v>469</v>
       </c>
       <c r="D163">
         <v>235379582</v>
       </c>
       <c r="E163" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F163" t="s">
         <v>106</v>
@@ -41569,16 +41566,16 @@
         <v>82</v>
       </c>
       <c r="BO163" t="s">
+        <v>484</v>
+      </c>
+      <c r="BP163" t="s">
+        <v>82</v>
+      </c>
+      <c r="BQ163" t="s">
         <v>485</v>
       </c>
-      <c r="BP163" t="s">
-        <v>82</v>
-      </c>
-      <c r="BQ163" t="s">
+      <c r="BR163" t="s">
         <v>486</v>
-      </c>
-      <c r="BR163" t="s">
-        <v>487</v>
       </c>
       <c r="BS163">
         <v>0</v>
@@ -41610,16 +41607,16 @@
         <v>163</v>
       </c>
       <c r="B164" t="s">
+        <v>434</v>
+      </c>
+      <c r="C164" t="s">
         <v>435</v>
-      </c>
-      <c r="C164" t="s">
-        <v>436</v>
       </c>
       <c r="D164">
         <v>235696923</v>
       </c>
       <c r="E164" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="F164" t="s">
         <v>106</v>
@@ -41796,7 +41793,7 @@
         <v>0</v>
       </c>
       <c r="BL164" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="BM164">
         <v>28738478</v>
@@ -41805,16 +41802,16 @@
         <v>82</v>
       </c>
       <c r="BO164" t="s">
+        <v>489</v>
+      </c>
+      <c r="BP164" t="s">
+        <v>82</v>
+      </c>
+      <c r="BQ164" t="s">
+        <v>370</v>
+      </c>
+      <c r="BR164" t="s">
         <v>490</v>
-      </c>
-      <c r="BP164" t="s">
-        <v>82</v>
-      </c>
-      <c r="BQ164" t="s">
-        <v>371</v>
-      </c>
-      <c r="BR164" t="s">
-        <v>491</v>
       </c>
       <c r="BS164">
         <v>NaN</v>
@@ -41846,16 +41843,16 @@
         <v>164</v>
       </c>
       <c r="B165" t="s">
+        <v>467</v>
+      </c>
+      <c r="C165" t="s">
         <v>468</v>
-      </c>
-      <c r="C165" t="s">
-        <v>469</v>
       </c>
       <c r="D165">
         <v>235391669</v>
       </c>
       <c r="E165" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="F165" t="s">
         <v>106</v>
@@ -42082,16 +42079,16 @@
         <v>165</v>
       </c>
       <c r="B166" t="s">
+        <v>467</v>
+      </c>
+      <c r="C166" t="s">
         <v>468</v>
-      </c>
-      <c r="C166" t="s">
-        <v>469</v>
       </c>
       <c r="D166">
         <v>235365158</v>
       </c>
       <c r="E166" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="F166" t="s">
         <v>138</v>
@@ -42318,16 +42315,16 @@
         <v>166</v>
       </c>
       <c r="B167" t="s">
+        <v>467</v>
+      </c>
+      <c r="C167" t="s">
         <v>468</v>
-      </c>
-      <c r="C167" t="s">
-        <v>469</v>
       </c>
       <c r="D167">
         <v>235418019</v>
       </c>
       <c r="E167" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="F167" t="s">
         <v>138</v>
@@ -42554,16 +42551,16 @@
         <v>167</v>
       </c>
       <c r="B168" t="s">
+        <v>467</v>
+      </c>
+      <c r="C168" t="s">
         <v>468</v>
-      </c>
-      <c r="C168" t="s">
-        <v>469</v>
       </c>
       <c r="D168">
         <v>235369944</v>
       </c>
       <c r="E168" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="F168" t="s">
         <v>119</v>
@@ -42790,16 +42787,16 @@
         <v>168</v>
       </c>
       <c r="B169" t="s">
+        <v>467</v>
+      </c>
+      <c r="C169" t="s">
         <v>468</v>
-      </c>
-      <c r="C169" t="s">
-        <v>469</v>
       </c>
       <c r="D169">
         <v>235817496</v>
       </c>
       <c r="E169" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="F169" t="s">
         <v>81</v>
@@ -43026,16 +43023,16 @@
         <v>169</v>
       </c>
       <c r="B170" t="s">
+        <v>467</v>
+      </c>
+      <c r="C170" t="s">
         <v>468</v>
-      </c>
-      <c r="C170" t="s">
-        <v>469</v>
       </c>
       <c r="D170">
         <v>235479727</v>
       </c>
       <c r="E170" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="F170" t="s">
         <v>106</v>
@@ -43212,7 +43209,7 @@
         <v>0</v>
       </c>
       <c r="BL170" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="BM170">
         <v>263132854</v>
@@ -43221,16 +43218,16 @@
         <v>82</v>
       </c>
       <c r="BO170" t="s">
+        <v>498</v>
+      </c>
+      <c r="BP170" t="s">
+        <v>82</v>
+      </c>
+      <c r="BQ170" t="s">
         <v>499</v>
       </c>
-      <c r="BP170" t="s">
-        <v>82</v>
-      </c>
-      <c r="BQ170" t="s">
+      <c r="BR170" t="s">
         <v>500</v>
-      </c>
-      <c r="BR170" t="s">
-        <v>501</v>
       </c>
       <c r="BS170">
         <v>NaN</v>
@@ -43262,16 +43259,16 @@
         <v>170</v>
       </c>
       <c r="B171" t="s">
+        <v>501</v>
+      </c>
+      <c r="C171" t="s">
         <v>502</v>
-      </c>
-      <c r="C171" t="s">
-        <v>503</v>
       </c>
       <c r="D171">
         <v>235692753</v>
       </c>
       <c r="E171" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="F171" t="s">
         <v>81</v>
@@ -43448,7 +43445,7 @@
         <v>0</v>
       </c>
       <c r="BL171" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="BM171">
         <v>102150321</v>
@@ -43457,16 +43454,16 @@
         <v>82</v>
       </c>
       <c r="BO171" t="s">
+        <v>505</v>
+      </c>
+      <c r="BP171" t="s">
+        <v>82</v>
+      </c>
+      <c r="BQ171" t="s">
+        <v>354</v>
+      </c>
+      <c r="BR171" t="s">
         <v>506</v>
-      </c>
-      <c r="BP171" t="s">
-        <v>82</v>
-      </c>
-      <c r="BQ171" t="s">
-        <v>355</v>
-      </c>
-      <c r="BR171" t="s">
-        <v>507</v>
       </c>
       <c r="BS171">
         <v>NaN</v>
@@ -43498,22 +43495,22 @@
         <v>171</v>
       </c>
       <c r="B172" t="s">
+        <v>501</v>
+      </c>
+      <c r="C172" t="s">
         <v>502</v>
-      </c>
-      <c r="C172" t="s">
-        <v>503</v>
       </c>
       <c r="D172">
         <v>235401260</v>
       </c>
       <c r="E172" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="F172" t="s">
+        <v>292</v>
+      </c>
+      <c r="G172" t="s">
         <v>293</v>
-      </c>
-      <c r="G172" t="s">
-        <v>294</v>
       </c>
       <c r="H172">
         <v>8908924</v>
@@ -43734,16 +43731,16 @@
         <v>172</v>
       </c>
       <c r="B173" t="s">
+        <v>501</v>
+      </c>
+      <c r="C173" t="s">
         <v>502</v>
-      </c>
-      <c r="C173" t="s">
-        <v>503</v>
       </c>
       <c r="D173">
         <v>235449068</v>
       </c>
       <c r="E173" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="F173" t="s">
         <v>138</v>
@@ -43779,7 +43776,7 @@
         <v>1</v>
       </c>
       <c r="Q173" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="R173">
         <v>5</v>
@@ -43929,16 +43926,16 @@
         <v>82</v>
       </c>
       <c r="BO173" t="s">
+        <v>510</v>
+      </c>
+      <c r="BP173" t="s">
+        <v>82</v>
+      </c>
+      <c r="BQ173" t="s">
+        <v>341</v>
+      </c>
+      <c r="BR173" t="s">
         <v>511</v>
-      </c>
-      <c r="BP173" t="s">
-        <v>82</v>
-      </c>
-      <c r="BQ173" t="s">
-        <v>342</v>
-      </c>
-      <c r="BR173" t="s">
-        <v>512</v>
       </c>
       <c r="BS173">
         <v>0</v>
@@ -43970,16 +43967,16 @@
         <v>173</v>
       </c>
       <c r="B174" t="s">
+        <v>501</v>
+      </c>
+      <c r="C174" t="s">
         <v>502</v>
-      </c>
-      <c r="C174" t="s">
-        <v>503</v>
       </c>
       <c r="D174">
         <v>235535764</v>
       </c>
       <c r="E174" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="F174" t="s">
         <v>81</v>
@@ -44206,16 +44203,16 @@
         <v>174</v>
       </c>
       <c r="B175" t="s">
+        <v>501</v>
+      </c>
+      <c r="C175" t="s">
         <v>502</v>
-      </c>
-      <c r="C175" t="s">
-        <v>503</v>
       </c>
       <c r="D175">
         <v>235535027</v>
       </c>
       <c r="E175" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="F175" t="s">
         <v>106</v>
@@ -44442,16 +44439,16 @@
         <v>175</v>
       </c>
       <c r="B176" t="s">
+        <v>501</v>
+      </c>
+      <c r="C176" t="s">
         <v>502</v>
-      </c>
-      <c r="C176" t="s">
-        <v>503</v>
       </c>
       <c r="D176">
         <v>235415930</v>
       </c>
       <c r="E176" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="F176" t="s">
         <v>178</v>
@@ -44628,7 +44625,7 @@
         <v>0</v>
       </c>
       <c r="BL176" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="BM176">
         <v>259844096</v>
@@ -44637,16 +44634,16 @@
         <v>82</v>
       </c>
       <c r="BO176" t="s">
+        <v>516</v>
+      </c>
+      <c r="BP176" t="s">
+        <v>82</v>
+      </c>
+      <c r="BQ176" t="s">
+        <v>263</v>
+      </c>
+      <c r="BR176" t="s">
         <v>517</v>
-      </c>
-      <c r="BP176" t="s">
-        <v>82</v>
-      </c>
-      <c r="BQ176" t="s">
-        <v>264</v>
-      </c>
-      <c r="BR176" t="s">
-        <v>518</v>
       </c>
       <c r="BS176">
         <v>NaN</v>
@@ -44678,16 +44675,16 @@
         <v>176</v>
       </c>
       <c r="B177" t="s">
+        <v>501</v>
+      </c>
+      <c r="C177" t="s">
         <v>502</v>
-      </c>
-      <c r="C177" t="s">
-        <v>503</v>
       </c>
       <c r="D177">
         <v>235375146</v>
       </c>
       <c r="E177" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="F177" t="s">
         <v>94</v>
@@ -44914,16 +44911,16 @@
         <v>177</v>
       </c>
       <c r="B178" t="s">
+        <v>501</v>
+      </c>
+      <c r="C178" t="s">
         <v>502</v>
-      </c>
-      <c r="C178" t="s">
-        <v>503</v>
       </c>
       <c r="D178">
         <v>235364621</v>
       </c>
       <c r="E178" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="F178" t="s">
         <v>81</v>
@@ -45150,16 +45147,16 @@
         <v>178</v>
       </c>
       <c r="B179" t="s">
+        <v>501</v>
+      </c>
+      <c r="C179" t="s">
         <v>502</v>
-      </c>
-      <c r="C179" t="s">
-        <v>503</v>
       </c>
       <c r="D179">
         <v>235490397</v>
       </c>
       <c r="E179" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="F179" t="s">
         <v>138</v>
@@ -45386,16 +45383,16 @@
         <v>179</v>
       </c>
       <c r="B180" t="s">
+        <v>501</v>
+      </c>
+      <c r="C180" t="s">
         <v>502</v>
-      </c>
-      <c r="C180" t="s">
-        <v>503</v>
       </c>
       <c r="D180">
         <v>235702359</v>
       </c>
       <c r="E180" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="F180" t="s">
         <v>138</v>
@@ -45622,16 +45619,16 @@
         <v>180</v>
       </c>
       <c r="B181" t="s">
+        <v>434</v>
+      </c>
+      <c r="C181" t="s">
         <v>435</v>
-      </c>
-      <c r="C181" t="s">
-        <v>436</v>
       </c>
       <c r="D181">
         <v>235787453</v>
       </c>
       <c r="E181" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="F181" t="s">
         <v>106</v>
@@ -45808,7 +45805,7 @@
         <v>0</v>
       </c>
       <c r="BL181" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="BM181">
         <v>0</v>
@@ -45858,16 +45855,16 @@
         <v>181</v>
       </c>
       <c r="B182" t="s">
+        <v>524</v>
+      </c>
+      <c r="C182" t="s">
         <v>525</v>
-      </c>
-      <c r="C182" t="s">
-        <v>526</v>
       </c>
       <c r="D182">
         <v>235401756</v>
       </c>
       <c r="E182" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="F182" t="s">
         <v>106</v>
@@ -46094,16 +46091,16 @@
         <v>182</v>
       </c>
       <c r="B183" t="s">
+        <v>524</v>
+      </c>
+      <c r="C183" t="s">
         <v>525</v>
-      </c>
-      <c r="C183" t="s">
-        <v>526</v>
       </c>
       <c r="D183">
         <v>235401433</v>
       </c>
       <c r="E183" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="F183" t="s">
         <v>169</v>
@@ -46280,7 +46277,7 @@
         <v>0</v>
       </c>
       <c r="BL183" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="BM183">
         <v>263060810</v>
@@ -46289,16 +46286,16 @@
         <v>82</v>
       </c>
       <c r="BO183" t="s">
+        <v>529</v>
+      </c>
+      <c r="BP183" t="s">
+        <v>82</v>
+      </c>
+      <c r="BQ183" t="s">
+        <v>318</v>
+      </c>
+      <c r="BR183" t="s">
         <v>530</v>
-      </c>
-      <c r="BP183" t="s">
-        <v>82</v>
-      </c>
-      <c r="BQ183" t="s">
-        <v>319</v>
-      </c>
-      <c r="BR183" t="s">
-        <v>531</v>
       </c>
       <c r="BS183">
         <v>NaN</v>
@@ -46330,16 +46327,16 @@
         <v>183</v>
       </c>
       <c r="B184" t="s">
+        <v>524</v>
+      </c>
+      <c r="C184" t="s">
         <v>525</v>
-      </c>
-      <c r="C184" t="s">
-        <v>526</v>
       </c>
       <c r="D184">
         <v>235539923</v>
       </c>
       <c r="E184" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="F184" t="s">
         <v>106</v>
@@ -46566,16 +46563,16 @@
         <v>184</v>
       </c>
       <c r="B185" t="s">
+        <v>524</v>
+      </c>
+      <c r="C185" t="s">
         <v>525</v>
-      </c>
-      <c r="C185" t="s">
-        <v>526</v>
       </c>
       <c r="D185">
         <v>235693067</v>
       </c>
       <c r="E185" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="F185" t="s">
         <v>89</v>
@@ -46802,16 +46799,16 @@
         <v>185</v>
       </c>
       <c r="B186" t="s">
+        <v>524</v>
+      </c>
+      <c r="C186" t="s">
         <v>525</v>
-      </c>
-      <c r="C186" t="s">
-        <v>526</v>
       </c>
       <c r="D186">
         <v>235749316</v>
       </c>
       <c r="E186" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="F186" t="s">
         <v>106</v>
@@ -46988,7 +46985,7 @@
         <v>0</v>
       </c>
       <c r="BL186" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="BM186">
         <v>0</v>
@@ -47038,16 +47035,16 @@
         <v>186</v>
       </c>
       <c r="B187" t="s">
+        <v>524</v>
+      </c>
+      <c r="C187" t="s">
         <v>525</v>
-      </c>
-      <c r="C187" t="s">
-        <v>526</v>
       </c>
       <c r="D187">
         <v>235366829</v>
       </c>
       <c r="E187" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="F187" t="s">
         <v>138</v>
@@ -47224,7 +47221,7 @@
         <v>0</v>
       </c>
       <c r="BL187" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="BM187">
         <v>263025873</v>
@@ -47233,16 +47230,16 @@
         <v>82</v>
       </c>
       <c r="BO187" t="s">
+        <v>537</v>
+      </c>
+      <c r="BP187" t="s">
+        <v>82</v>
+      </c>
+      <c r="BQ187" t="s">
+        <v>370</v>
+      </c>
+      <c r="BR187" t="s">
         <v>538</v>
-      </c>
-      <c r="BP187" t="s">
-        <v>82</v>
-      </c>
-      <c r="BQ187" t="s">
-        <v>371</v>
-      </c>
-      <c r="BR187" t="s">
-        <v>539</v>
       </c>
       <c r="BS187">
         <v>NaN</v>
@@ -47274,22 +47271,22 @@
         <v>187</v>
       </c>
       <c r="B188" t="s">
+        <v>539</v>
+      </c>
+      <c r="C188" t="s">
         <v>540</v>
-      </c>
-      <c r="C188" t="s">
-        <v>541</v>
       </c>
       <c r="D188">
         <v>235696353</v>
       </c>
       <c r="E188" t="s">
+        <v>541</v>
+      </c>
+      <c r="F188" t="s">
         <v>542</v>
       </c>
-      <c r="F188" t="s">
+      <c r="G188" t="s">
         <v>543</v>
-      </c>
-      <c r="G188" t="s">
-        <v>544</v>
       </c>
       <c r="H188">
         <v>8910240</v>
@@ -47510,16 +47507,16 @@
         <v>188</v>
       </c>
       <c r="B189" t="s">
+        <v>524</v>
+      </c>
+      <c r="C189" t="s">
         <v>525</v>
-      </c>
-      <c r="C189" t="s">
-        <v>526</v>
       </c>
       <c r="D189">
         <v>235723482</v>
       </c>
       <c r="E189" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="F189" t="s">
         <v>94</v>
@@ -47696,7 +47693,7 @@
         <v>0</v>
       </c>
       <c r="BL189" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="BM189">
         <v>263393105</v>
@@ -47705,7 +47702,7 @@
         <v>82</v>
       </c>
       <c r="BO189" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="BP189" t="s">
         <v>82</v>
@@ -47714,7 +47711,7 @@
         <v>130</v>
       </c>
       <c r="BR189" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="BS189">
         <v>NaN</v>
@@ -47746,16 +47743,16 @@
         <v>189</v>
       </c>
       <c r="B190" t="s">
+        <v>524</v>
+      </c>
+      <c r="C190" t="s">
         <v>525</v>
-      </c>
-      <c r="C190" t="s">
-        <v>526</v>
       </c>
       <c r="D190">
         <v>235376693</v>
       </c>
       <c r="E190" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="F190" t="s">
         <v>106</v>
@@ -47982,16 +47979,16 @@
         <v>190</v>
       </c>
       <c r="B191" t="s">
+        <v>539</v>
+      </c>
+      <c r="C191" t="s">
         <v>540</v>
-      </c>
-      <c r="C191" t="s">
-        <v>541</v>
       </c>
       <c r="D191">
         <v>235693052</v>
       </c>
       <c r="E191" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="F191" t="s">
         <v>138</v>
@@ -48168,7 +48165,7 @@
         <v>0</v>
       </c>
       <c r="BL191" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="BM191">
         <v>263336055</v>
@@ -48177,16 +48174,16 @@
         <v>82</v>
       </c>
       <c r="BO191" t="s">
+        <v>551</v>
+      </c>
+      <c r="BP191" t="s">
+        <v>82</v>
+      </c>
+      <c r="BQ191" t="s">
+        <v>318</v>
+      </c>
+      <c r="BR191" t="s">
         <v>552</v>
-      </c>
-      <c r="BP191" t="s">
-        <v>82</v>
-      </c>
-      <c r="BQ191" t="s">
-        <v>319</v>
-      </c>
-      <c r="BR191" t="s">
-        <v>553</v>
       </c>
       <c r="BS191">
         <v>NaN</v>
@@ -48218,16 +48215,16 @@
         <v>191</v>
       </c>
       <c r="B192" t="s">
+        <v>539</v>
+      </c>
+      <c r="C192" t="s">
         <v>540</v>
-      </c>
-      <c r="C192" t="s">
-        <v>541</v>
       </c>
       <c r="D192">
         <v>235365982</v>
       </c>
       <c r="E192" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="F192" t="s">
         <v>106</v>
@@ -48454,16 +48451,16 @@
         <v>192</v>
       </c>
       <c r="B193" t="s">
+        <v>539</v>
+      </c>
+      <c r="C193" t="s">
         <v>540</v>
-      </c>
-      <c r="C193" t="s">
-        <v>541</v>
       </c>
       <c r="D193">
         <v>235873623</v>
       </c>
       <c r="E193" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="F193" t="s">
         <v>106</v>
@@ -48690,22 +48687,22 @@
         <v>193</v>
       </c>
       <c r="B194" t="s">
+        <v>539</v>
+      </c>
+      <c r="C194" t="s">
         <v>540</v>
-      </c>
-      <c r="C194" t="s">
-        <v>541</v>
       </c>
       <c r="D194">
         <v>235696232</v>
       </c>
       <c r="E194" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="F194" t="s">
+        <v>297</v>
+      </c>
+      <c r="G194" t="s">
         <v>298</v>
-      </c>
-      <c r="G194" t="s">
-        <v>299</v>
       </c>
       <c r="H194">
         <v>8908959</v>
@@ -48926,16 +48923,16 @@
         <v>194</v>
       </c>
       <c r="B195" t="s">
+        <v>539</v>
+      </c>
+      <c r="C195" t="s">
         <v>540</v>
-      </c>
-      <c r="C195" t="s">
-        <v>541</v>
       </c>
       <c r="D195">
         <v>235364978</v>
       </c>
       <c r="E195" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="F195" t="s">
         <v>106</v>
@@ -49162,16 +49159,16 @@
         <v>195</v>
       </c>
       <c r="B196" t="s">
+        <v>539</v>
+      </c>
+      <c r="C196" t="s">
         <v>540</v>
-      </c>
-      <c r="C196" t="s">
-        <v>541</v>
       </c>
       <c r="D196">
         <v>235693385</v>
       </c>
       <c r="E196" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="F196" t="s">
         <v>81</v>
@@ -49398,22 +49395,22 @@
         <v>196</v>
       </c>
       <c r="B197" t="s">
+        <v>539</v>
+      </c>
+      <c r="C197" t="s">
         <v>540</v>
-      </c>
-      <c r="C197" t="s">
-        <v>541</v>
       </c>
       <c r="D197">
         <v>235362830</v>
       </c>
       <c r="E197" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="F197" t="s">
+        <v>297</v>
+      </c>
+      <c r="G197" t="s">
         <v>298</v>
-      </c>
-      <c r="G197" t="s">
-        <v>299</v>
       </c>
       <c r="H197">
         <v>8908959</v>
@@ -49634,16 +49631,16 @@
         <v>197</v>
       </c>
       <c r="B198" t="s">
+        <v>539</v>
+      </c>
+      <c r="C198" t="s">
         <v>540</v>
-      </c>
-      <c r="C198" t="s">
-        <v>541</v>
       </c>
       <c r="D198">
         <v>235398434</v>
       </c>
       <c r="E198" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="F198" t="s">
         <v>138</v>
@@ -49870,16 +49867,16 @@
         <v>198</v>
       </c>
       <c r="B199" t="s">
+        <v>539</v>
+      </c>
+      <c r="C199" t="s">
         <v>540</v>
-      </c>
-      <c r="C199" t="s">
-        <v>541</v>
       </c>
       <c r="D199">
         <v>235416947</v>
       </c>
       <c r="E199" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="F199" t="s">
         <v>94</v>
@@ -50106,16 +50103,16 @@
         <v>199</v>
       </c>
       <c r="B200" t="s">
+        <v>434</v>
+      </c>
+      <c r="C200" t="s">
         <v>435</v>
-      </c>
-      <c r="C200" t="s">
-        <v>436</v>
       </c>
       <c r="D200">
         <v>235274618</v>
       </c>
       <c r="E200" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="F200" t="s">
         <v>119</v>
@@ -50301,22 +50298,22 @@
         <v>82</v>
       </c>
       <c r="BO200" t="s">
+        <v>562</v>
+      </c>
+      <c r="BP200" t="s">
+        <v>82</v>
+      </c>
+      <c r="BQ200" t="s">
+        <v>263</v>
+      </c>
+      <c r="BR200" t="s">
         <v>563</v>
-      </c>
-      <c r="BP200" t="s">
-        <v>82</v>
-      </c>
-      <c r="BQ200" t="s">
-        <v>264</v>
-      </c>
-      <c r="BR200" t="s">
-        <v>564</v>
       </c>
       <c r="BS200">
         <v>NaN</v>
       </c>
       <c r="BT200" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="BU200" t="s">
         <v>82</v>
@@ -50342,16 +50339,16 @@
         <v>200</v>
       </c>
       <c r="B201" t="s">
+        <v>434</v>
+      </c>
+      <c r="C201" t="s">
         <v>435</v>
-      </c>
-      <c r="C201" t="s">
-        <v>436</v>
       </c>
       <c r="D201">
         <v>235716923</v>
       </c>
       <c r="E201" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="F201" t="s">
         <v>138</v>
@@ -50528,7 +50525,7 @@
         <v>0</v>
       </c>
       <c r="BL201" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="BM201">
         <v>29591</v>
@@ -50537,7 +50534,7 @@
         <v>82</v>
       </c>
       <c r="BO201" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="BP201" t="s">
         <v>82</v>
@@ -50546,13 +50543,13 @@
         <v>111</v>
       </c>
       <c r="BR201" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="BS201">
         <v>NaN</v>
       </c>
       <c r="BT201" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="BU201" t="s">
         <v>82</v>
@@ -50578,22 +50575,22 @@
         <v>201</v>
       </c>
       <c r="B202" t="s">
+        <v>388</v>
+      </c>
+      <c r="C202" t="s">
         <v>389</v>
-      </c>
-      <c r="C202" t="s">
-        <v>390</v>
       </c>
       <c r="D202">
         <v>235367130</v>
       </c>
       <c r="E202" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="F202" t="s">
+        <v>292</v>
+      </c>
+      <c r="G202" t="s">
         <v>293</v>
-      </c>
-      <c r="G202" t="s">
-        <v>294</v>
       </c>
       <c r="H202">
         <v>8908924</v>
@@ -50764,7 +50761,7 @@
         <v>0</v>
       </c>
       <c r="BL202" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="BM202">
         <v>205922571</v>
@@ -50773,16 +50770,16 @@
         <v>82</v>
       </c>
       <c r="BO202" t="s">
+        <v>572</v>
+      </c>
+      <c r="BP202" t="s">
+        <v>82</v>
+      </c>
+      <c r="BQ202" t="s">
+        <v>449</v>
+      </c>
+      <c r="BR202" t="s">
         <v>573</v>
-      </c>
-      <c r="BP202" t="s">
-        <v>82</v>
-      </c>
-      <c r="BQ202" t="s">
-        <v>450</v>
-      </c>
-      <c r="BR202" t="s">
-        <v>574</v>
       </c>
       <c r="BS202">
         <v>NaN</v>
@@ -50814,16 +50811,16 @@
         <v>202</v>
       </c>
       <c r="B203" t="s">
+        <v>388</v>
+      </c>
+      <c r="C203" t="s">
         <v>389</v>
-      </c>
-      <c r="C203" t="s">
-        <v>390</v>
       </c>
       <c r="D203">
         <v>235364509</v>
       </c>
       <c r="E203" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="F203" t="s">
         <v>138</v>
@@ -51000,7 +50997,7 @@
         <v>0</v>
       </c>
       <c r="BL203" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="BM203">
         <v>246931553</v>
@@ -51009,7 +51006,7 @@
         <v>82</v>
       </c>
       <c r="BO203" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="BP203" t="s">
         <v>82</v>
@@ -51018,7 +51015,7 @@
         <v>188</v>
       </c>
       <c r="BR203" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="BS203">
         <v>NaN</v>
@@ -51050,16 +51047,16 @@
         <v>203</v>
       </c>
       <c r="B204" t="s">
+        <v>388</v>
+      </c>
+      <c r="C204" t="s">
         <v>389</v>
-      </c>
-      <c r="C204" t="s">
-        <v>390</v>
       </c>
       <c r="D204">
         <v>235371024</v>
       </c>
       <c r="E204" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="F204" t="s">
         <v>138</v>
@@ -51286,16 +51283,16 @@
         <v>204</v>
       </c>
       <c r="B205" t="s">
+        <v>388</v>
+      </c>
+      <c r="C205" t="s">
         <v>389</v>
-      </c>
-      <c r="C205" t="s">
-        <v>390</v>
       </c>
       <c r="D205">
         <v>235362721</v>
       </c>
       <c r="E205" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="F205" t="s">
         <v>138</v>
@@ -51522,16 +51519,16 @@
         <v>205</v>
       </c>
       <c r="B206" t="s">
+        <v>388</v>
+      </c>
+      <c r="C206" t="s">
         <v>389</v>
-      </c>
-      <c r="C206" t="s">
-        <v>390</v>
       </c>
       <c r="D206">
         <v>235388386</v>
       </c>
       <c r="E206" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="F206" t="s">
         <v>106</v>
@@ -51758,16 +51755,16 @@
         <v>206</v>
       </c>
       <c r="B207" t="s">
+        <v>388</v>
+      </c>
+      <c r="C207" t="s">
         <v>389</v>
-      </c>
-      <c r="C207" t="s">
-        <v>390</v>
       </c>
       <c r="D207">
         <v>235375123</v>
       </c>
       <c r="E207" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="F207" t="s">
         <v>178</v>
@@ -51944,7 +51941,7 @@
         <v>0</v>
       </c>
       <c r="BL207" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="BM207">
         <v>0</v>
@@ -51994,16 +51991,16 @@
         <v>207</v>
       </c>
       <c r="B208" t="s">
+        <v>388</v>
+      </c>
+      <c r="C208" t="s">
         <v>389</v>
-      </c>
-      <c r="C208" t="s">
-        <v>390</v>
       </c>
       <c r="D208">
         <v>235394375</v>
       </c>
       <c r="E208" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="F208" t="s">
         <v>138</v>
@@ -52039,7 +52036,7 @@
         <v>1</v>
       </c>
       <c r="Q208" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="R208">
         <v>11</v>
@@ -52230,16 +52227,16 @@
         <v>208</v>
       </c>
       <c r="B209" t="s">
+        <v>585</v>
+      </c>
+      <c r="C209" t="s">
         <v>586</v>
-      </c>
-      <c r="C209" t="s">
-        <v>587</v>
       </c>
       <c r="D209">
         <v>235429359</v>
       </c>
       <c r="E209" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="F209" t="s">
         <v>106</v>
@@ -52416,7 +52413,7 @@
         <v>0</v>
       </c>
       <c r="BL209" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="BM209">
         <v>262459936</v>
@@ -52425,16 +52422,16 @@
         <v>82</v>
       </c>
       <c r="BO209" t="s">
+        <v>589</v>
+      </c>
+      <c r="BP209" t="s">
+        <v>82</v>
+      </c>
+      <c r="BQ209" t="s">
         <v>590</v>
       </c>
-      <c r="BP209" t="s">
-        <v>82</v>
-      </c>
-      <c r="BQ209" t="s">
+      <c r="BR209" t="s">
         <v>591</v>
-      </c>
-      <c r="BR209" t="s">
-        <v>592</v>
       </c>
       <c r="BS209">
         <v>NaN</v>
@@ -52466,16 +52463,16 @@
         <v>209</v>
       </c>
       <c r="B210" t="s">
+        <v>388</v>
+      </c>
+      <c r="C210" t="s">
         <v>389</v>
-      </c>
-      <c r="C210" t="s">
-        <v>390</v>
       </c>
       <c r="D210">
         <v>235709038</v>
       </c>
       <c r="E210" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="F210" t="s">
         <v>81</v>
@@ -52702,22 +52699,22 @@
         <v>210</v>
       </c>
       <c r="B211" t="s">
+        <v>585</v>
+      </c>
+      <c r="C211" t="s">
         <v>586</v>
-      </c>
-      <c r="C211" t="s">
-        <v>587</v>
       </c>
       <c r="D211">
         <v>235363470</v>
       </c>
       <c r="E211" t="s">
+        <v>593</v>
+      </c>
+      <c r="F211" t="s">
         <v>594</v>
       </c>
-      <c r="F211" t="s">
+      <c r="G211" t="s">
         <v>595</v>
-      </c>
-      <c r="G211" t="s">
-        <v>596</v>
       </c>
       <c r="H211">
         <v>8910948</v>
@@ -52747,7 +52744,7 @@
         <v>1</v>
       </c>
       <c r="Q211" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="R211">
         <v>10</v>
@@ -52888,7 +52885,7 @@
         <v>0</v>
       </c>
       <c r="BL211" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="BM211">
         <v>233190612</v>
@@ -52897,16 +52894,16 @@
         <v>82</v>
       </c>
       <c r="BO211" t="s">
+        <v>597</v>
+      </c>
+      <c r="BP211" t="s">
+        <v>82</v>
+      </c>
+      <c r="BQ211" t="s">
+        <v>341</v>
+      </c>
+      <c r="BR211" t="s">
         <v>598</v>
-      </c>
-      <c r="BP211" t="s">
-        <v>82</v>
-      </c>
-      <c r="BQ211" t="s">
-        <v>342</v>
-      </c>
-      <c r="BR211" t="s">
-        <v>599</v>
       </c>
       <c r="BS211">
         <v>NaN</v>
@@ -52938,16 +52935,16 @@
         <v>211</v>
       </c>
       <c r="B212" t="s">
+        <v>585</v>
+      </c>
+      <c r="C212" t="s">
         <v>586</v>
-      </c>
-      <c r="C212" t="s">
-        <v>587</v>
       </c>
       <c r="D212">
         <v>235698934</v>
       </c>
       <c r="E212" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="F212" t="s">
         <v>94</v>
@@ -53124,7 +53121,7 @@
         <v>0</v>
       </c>
       <c r="BL212" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="BM212">
         <v>0</v>
@@ -53174,16 +53171,16 @@
         <v>212</v>
       </c>
       <c r="B213" t="s">
+        <v>585</v>
+      </c>
+      <c r="C213" t="s">
         <v>586</v>
-      </c>
-      <c r="C213" t="s">
-        <v>587</v>
       </c>
       <c r="D213">
         <v>235807291</v>
       </c>
       <c r="E213" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="F213" t="s">
         <v>106</v>
@@ -53360,7 +53357,7 @@
         <v>0</v>
       </c>
       <c r="BL213" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="BM213">
         <v>263438413</v>
@@ -53369,7 +53366,7 @@
         <v>82</v>
       </c>
       <c r="BO213" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="BP213" t="s">
         <v>82</v>
@@ -53378,7 +53375,7 @@
         <v>229</v>
       </c>
       <c r="BR213" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="BS213">
         <v>NaN</v>
@@ -53410,16 +53407,16 @@
         <v>213</v>
       </c>
       <c r="B214" t="s">
+        <v>585</v>
+      </c>
+      <c r="C214" t="s">
         <v>586</v>
-      </c>
-      <c r="C214" t="s">
-        <v>587</v>
       </c>
       <c r="D214">
         <v>235703708</v>
       </c>
       <c r="E214" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="F214" t="s">
         <v>138</v>
@@ -53596,7 +53593,7 @@
         <v>0</v>
       </c>
       <c r="BL214" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="BM214">
         <v>0</v>
@@ -53646,22 +53643,22 @@
         <v>214</v>
       </c>
       <c r="B215" t="s">
+        <v>585</v>
+      </c>
+      <c r="C215" t="s">
         <v>586</v>
-      </c>
-      <c r="C215" t="s">
-        <v>587</v>
       </c>
       <c r="D215">
         <v>235379808</v>
       </c>
       <c r="E215" t="s">
+        <v>607</v>
+      </c>
+      <c r="F215" t="s">
         <v>608</v>
       </c>
-      <c r="F215" t="s">
+      <c r="G215" t="s">
         <v>609</v>
-      </c>
-      <c r="G215" t="s">
-        <v>610</v>
       </c>
       <c r="H215">
         <v>8909496</v>
@@ -53841,7 +53838,7 @@
         <v>82</v>
       </c>
       <c r="BO215" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="BP215" t="s">
         <v>82</v>
@@ -53850,7 +53847,7 @@
         <v>241</v>
       </c>
       <c r="BR215" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="BS215">
         <v>0</v>
@@ -53882,16 +53879,16 @@
         <v>215</v>
       </c>
       <c r="B216" t="s">
+        <v>585</v>
+      </c>
+      <c r="C216" t="s">
         <v>586</v>
-      </c>
-      <c r="C216" t="s">
-        <v>587</v>
       </c>
       <c r="D216">
         <v>235467069</v>
       </c>
       <c r="E216" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="F216" t="s">
         <v>178</v>
@@ -54068,7 +54065,7 @@
         <v>0</v>
       </c>
       <c r="BL216" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="BM216">
         <v>217320404</v>
@@ -54077,7 +54074,7 @@
         <v>82</v>
       </c>
       <c r="BO216" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="BP216" t="s">
         <v>82</v>
@@ -54086,7 +54083,7 @@
         <v>193</v>
       </c>
       <c r="BR216" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="BS216">
         <v>NaN</v>
@@ -54118,16 +54115,16 @@
         <v>216</v>
       </c>
       <c r="B217" t="s">
+        <v>585</v>
+      </c>
+      <c r="C217" t="s">
         <v>586</v>
-      </c>
-      <c r="C217" t="s">
-        <v>587</v>
       </c>
       <c r="D217">
         <v>235396098</v>
       </c>
       <c r="E217" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="F217" t="s">
         <v>138</v>
@@ -54304,7 +54301,7 @@
         <v>0</v>
       </c>
       <c r="BL217" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="BM217">
         <v>244494122</v>
@@ -54313,16 +54310,16 @@
         <v>82</v>
       </c>
       <c r="BO217" t="s">
+        <v>618</v>
+      </c>
+      <c r="BP217" t="s">
+        <v>82</v>
+      </c>
+      <c r="BQ217" t="s">
+        <v>449</v>
+      </c>
+      <c r="BR217" t="s">
         <v>619</v>
-      </c>
-      <c r="BP217" t="s">
-        <v>82</v>
-      </c>
-      <c r="BQ217" t="s">
-        <v>450</v>
-      </c>
-      <c r="BR217" t="s">
-        <v>620</v>
       </c>
       <c r="BS217">
         <v>NaN</v>
@@ -54354,16 +54351,16 @@
         <v>217</v>
       </c>
       <c r="B218" t="s">
+        <v>585</v>
+      </c>
+      <c r="C218" t="s">
         <v>586</v>
-      </c>
-      <c r="C218" t="s">
-        <v>587</v>
       </c>
       <c r="D218">
         <v>235692629</v>
       </c>
       <c r="E218" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="F218" t="s">
         <v>138</v>
@@ -54540,7 +54537,7 @@
         <v>0</v>
       </c>
       <c r="BL218" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="BM218">
         <v>258159295</v>
@@ -54549,16 +54546,16 @@
         <v>82</v>
       </c>
       <c r="BO218" t="s">
+        <v>622</v>
+      </c>
+      <c r="BP218" t="s">
+        <v>82</v>
+      </c>
+      <c r="BQ218" t="s">
+        <v>354</v>
+      </c>
+      <c r="BR218" t="s">
         <v>623</v>
-      </c>
-      <c r="BP218" t="s">
-        <v>82</v>
-      </c>
-      <c r="BQ218" t="s">
-        <v>355</v>
-      </c>
-      <c r="BR218" t="s">
-        <v>624</v>
       </c>
       <c r="BS218">
         <v>NaN</v>
@@ -54590,16 +54587,16 @@
         <v>218</v>
       </c>
       <c r="B219" t="s">
+        <v>585</v>
+      </c>
+      <c r="C219" t="s">
         <v>586</v>
-      </c>
-      <c r="C219" t="s">
-        <v>587</v>
       </c>
       <c r="D219">
         <v>235365704</v>
       </c>
       <c r="E219" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="F219" t="s">
         <v>106</v>
@@ -54826,16 +54823,16 @@
         <v>219</v>
       </c>
       <c r="B220" t="s">
+        <v>434</v>
+      </c>
+      <c r="C220" t="s">
         <v>435</v>
-      </c>
-      <c r="C220" t="s">
-        <v>436</v>
       </c>
       <c r="D220">
         <v>235387701</v>
       </c>
       <c r="E220" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="F220" t="s">
         <v>178</v>
@@ -55062,16 +55059,16 @@
         <v>220</v>
       </c>
       <c r="B221" t="s">
+        <v>434</v>
+      </c>
+      <c r="C221" t="s">
         <v>435</v>
-      </c>
-      <c r="C221" t="s">
-        <v>436</v>
       </c>
       <c r="D221">
         <v>235697230</v>
       </c>
       <c r="E221" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="F221" t="s">
         <v>163</v>
@@ -55298,16 +55295,16 @@
         <v>221</v>
       </c>
       <c r="B222" t="s">
+        <v>434</v>
+      </c>
+      <c r="C222" t="s">
         <v>435</v>
-      </c>
-      <c r="C222" t="s">
-        <v>436</v>
       </c>
       <c r="D222">
         <v>235746137</v>
       </c>
       <c r="E222" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="F222" t="s">
         <v>163</v>
@@ -55484,7 +55481,7 @@
         <v>0</v>
       </c>
       <c r="BL222" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="BM222">
         <v>0</v>
@@ -55534,16 +55531,16 @@
         <v>222</v>
       </c>
       <c r="B223" t="s">
+        <v>434</v>
+      </c>
+      <c r="C223" t="s">
         <v>435</v>
-      </c>
-      <c r="C223" t="s">
-        <v>436</v>
       </c>
       <c r="D223">
         <v>235697730</v>
       </c>
       <c r="E223" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="F223" t="s">
         <v>106</v>
@@ -55744,7 +55741,7 @@
         <v>0</v>
       </c>
       <c r="BT223" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="BU223" t="s">
         <v>82</v>
@@ -55770,16 +55767,16 @@
         <v>223</v>
       </c>
       <c r="B224" t="s">
+        <v>434</v>
+      </c>
+      <c r="C224" t="s">
         <v>435</v>
-      </c>
-      <c r="C224" t="s">
-        <v>436</v>
       </c>
       <c r="D224">
         <v>235363721</v>
       </c>
       <c r="E224" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="F224" t="s">
         <v>138</v>
@@ -55956,7 +55953,7 @@
         <v>0</v>
       </c>
       <c r="BL224" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="BM224">
         <v>0</v>
@@ -56006,16 +56003,16 @@
         <v>224</v>
       </c>
       <c r="B225" t="s">
+        <v>434</v>
+      </c>
+      <c r="C225" t="s">
         <v>435</v>
-      </c>
-      <c r="C225" t="s">
-        <v>436</v>
       </c>
       <c r="D225">
         <v>235364623</v>
       </c>
       <c r="E225" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="F225" t="s">
         <v>178</v>
@@ -56242,16 +56239,16 @@
         <v>225</v>
       </c>
       <c r="B226" t="s">
+        <v>434</v>
+      </c>
+      <c r="C226" t="s">
         <v>435</v>
-      </c>
-      <c r="C226" t="s">
-        <v>436</v>
       </c>
       <c r="D226">
         <v>235762527</v>
       </c>
       <c r="E226" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="F226" t="s">
         <v>163</v>
@@ -56428,7 +56425,7 @@
         <v>0</v>
       </c>
       <c r="BL226" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="BM226">
         <v>0</v>
@@ -56478,16 +56475,16 @@
         <v>226</v>
       </c>
       <c r="B227" t="s">
+        <v>434</v>
+      </c>
+      <c r="C227" t="s">
         <v>435</v>
-      </c>
-      <c r="C227" t="s">
-        <v>436</v>
       </c>
       <c r="D227">
         <v>235468982</v>
       </c>
       <c r="E227" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="F227" t="s">
         <v>178</v>
@@ -56714,16 +56711,16 @@
         <v>227</v>
       </c>
       <c r="B228" t="s">
+        <v>434</v>
+      </c>
+      <c r="C228" t="s">
         <v>435</v>
-      </c>
-      <c r="C228" t="s">
-        <v>436</v>
       </c>
       <c r="D228">
         <v>235380952</v>
       </c>
       <c r="E228" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="F228" t="s">
         <v>178</v>
@@ -56950,16 +56947,16 @@
         <v>228</v>
       </c>
       <c r="B229" t="s">
+        <v>434</v>
+      </c>
+      <c r="C229" t="s">
         <v>435</v>
-      </c>
-      <c r="C229" t="s">
-        <v>436</v>
       </c>
       <c r="D229">
         <v>235693755</v>
       </c>
       <c r="E229" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="F229" t="s">
         <v>81</v>
@@ -57136,7 +57133,7 @@
         <v>0</v>
       </c>
       <c r="BL229" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="BM229">
         <v>229126825</v>
@@ -57145,16 +57142,16 @@
         <v>82</v>
       </c>
       <c r="BO229" t="s">
+        <v>640</v>
+      </c>
+      <c r="BP229" t="s">
+        <v>82</v>
+      </c>
+      <c r="BQ229" t="s">
+        <v>354</v>
+      </c>
+      <c r="BR229" t="s">
         <v>641</v>
-      </c>
-      <c r="BP229" t="s">
-        <v>82</v>
-      </c>
-      <c r="BQ229" t="s">
-        <v>355</v>
-      </c>
-      <c r="BR229" t="s">
-        <v>642</v>
       </c>
       <c r="BS229">
         <v>NaN</v>
@@ -57186,16 +57183,16 @@
         <v>229</v>
       </c>
       <c r="B230" t="s">
+        <v>434</v>
+      </c>
+      <c r="C230" t="s">
         <v>435</v>
-      </c>
-      <c r="C230" t="s">
-        <v>436</v>
       </c>
       <c r="D230">
         <v>235366450</v>
       </c>
       <c r="E230" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="F230" t="s">
         <v>138</v>
@@ -57381,7 +57378,7 @@
         <v>82</v>
       </c>
       <c r="BO230" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="BP230" t="s">
         <v>82</v>
@@ -57390,13 +57387,13 @@
         <v>175</v>
       </c>
       <c r="BR230" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="BS230">
         <v>NaN</v>
       </c>
       <c r="BT230" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="BU230" t="s">
         <v>82</v>
@@ -57422,16 +57419,16 @@
         <v>230</v>
       </c>
       <c r="B231" t="s">
+        <v>434</v>
+      </c>
+      <c r="C231" t="s">
         <v>435</v>
-      </c>
-      <c r="C231" t="s">
-        <v>436</v>
       </c>
       <c r="D231">
         <v>235517942</v>
       </c>
       <c r="E231" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="F231" t="s">
         <v>138</v>
@@ -57608,7 +57605,7 @@
         <v>0</v>
       </c>
       <c r="BL231" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="BM231">
         <v>263139669</v>
@@ -57617,16 +57614,16 @@
         <v>82</v>
       </c>
       <c r="BO231" t="s">
+        <v>647</v>
+      </c>
+      <c r="BP231" t="s">
+        <v>82</v>
+      </c>
+      <c r="BQ231" t="s">
+        <v>499</v>
+      </c>
+      <c r="BR231" t="s">
         <v>648</v>
-      </c>
-      <c r="BP231" t="s">
-        <v>82</v>
-      </c>
-      <c r="BQ231" t="s">
-        <v>500</v>
-      </c>
-      <c r="BR231" t="s">
-        <v>649</v>
       </c>
       <c r="BS231">
         <v>NaN</v>
@@ -57658,16 +57655,16 @@
         <v>231</v>
       </c>
       <c r="B232" t="s">
+        <v>434</v>
+      </c>
+      <c r="C232" t="s">
         <v>435</v>
-      </c>
-      <c r="C232" t="s">
-        <v>436</v>
       </c>
       <c r="D232">
         <v>235694114</v>
       </c>
       <c r="E232" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="F232" t="s">
         <v>106</v>
@@ -57844,7 +57841,7 @@
         <v>0</v>
       </c>
       <c r="BL232" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="BM232">
         <v>263329270</v>
@@ -57853,7 +57850,7 @@
         <v>82</v>
       </c>
       <c r="BO232" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="BP232" t="s">
         <v>82</v>
@@ -57862,13 +57859,13 @@
         <v>111</v>
       </c>
       <c r="BR232" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="BS232">
         <v>NaN</v>
       </c>
       <c r="BT232" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="BU232" t="s">
         <v>82</v>
@@ -57894,16 +57891,16 @@
         <v>232</v>
       </c>
       <c r="B233" t="s">
+        <v>434</v>
+      </c>
+      <c r="C233" t="s">
         <v>435</v>
-      </c>
-      <c r="C233" t="s">
-        <v>436</v>
       </c>
       <c r="D233">
         <v>235694013</v>
       </c>
       <c r="E233" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="F233" t="s">
         <v>138</v>
@@ -58089,22 +58086,22 @@
         <v>82</v>
       </c>
       <c r="BO233" t="s">
+        <v>654</v>
+      </c>
+      <c r="BP233" t="s">
+        <v>82</v>
+      </c>
+      <c r="BQ233" t="s">
+        <v>333</v>
+      </c>
+      <c r="BR233" t="s">
         <v>655</v>
-      </c>
-      <c r="BP233" t="s">
-        <v>82</v>
-      </c>
-      <c r="BQ233" t="s">
-        <v>334</v>
-      </c>
-      <c r="BR233" t="s">
-        <v>656</v>
       </c>
       <c r="BS233">
         <v>NaN</v>
       </c>
       <c r="BT233" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="BU233" t="s">
         <v>82</v>
@@ -58130,22 +58127,22 @@
         <v>233</v>
       </c>
       <c r="B234" t="s">
+        <v>434</v>
+      </c>
+      <c r="C234" t="s">
         <v>435</v>
-      </c>
-      <c r="C234" t="s">
-        <v>436</v>
       </c>
       <c r="D234">
         <v>235409817</v>
       </c>
       <c r="E234" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="F234" t="s">
+        <v>292</v>
+      </c>
+      <c r="G234" t="s">
         <v>293</v>
-      </c>
-      <c r="G234" t="s">
-        <v>294</v>
       </c>
       <c r="H234">
         <v>8908924</v>
@@ -58175,7 +58172,7 @@
         <v>1</v>
       </c>
       <c r="Q234" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="R234">
         <v>5</v>
@@ -58340,7 +58337,7 @@
         <v>0</v>
       </c>
       <c r="BT234" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="BU234" t="s">
         <v>82</v>
@@ -58366,16 +58363,16 @@
         <v>234</v>
       </c>
       <c r="B235" t="s">
+        <v>434</v>
+      </c>
+      <c r="C235" t="s">
         <v>435</v>
-      </c>
-      <c r="C235" t="s">
-        <v>436</v>
       </c>
       <c r="D235">
         <v>235394414</v>
       </c>
       <c r="E235" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="F235" t="s">
         <v>106</v>
@@ -58552,7 +58549,7 @@
         <v>0</v>
       </c>
       <c r="BL235" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="BM235">
         <v>263041016</v>
@@ -58561,22 +58558,22 @@
         <v>82</v>
       </c>
       <c r="BO235" t="s">
+        <v>660</v>
+      </c>
+      <c r="BP235" t="s">
+        <v>82</v>
+      </c>
+      <c r="BQ235" t="s">
         <v>661</v>
       </c>
-      <c r="BP235" t="s">
-        <v>82</v>
-      </c>
-      <c r="BQ235" t="s">
+      <c r="BR235" t="s">
         <v>662</v>
-      </c>
-      <c r="BR235" t="s">
-        <v>663</v>
       </c>
       <c r="BS235">
         <v>NaN</v>
       </c>
       <c r="BT235" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="BU235" t="s">
         <v>82</v>
@@ -58602,16 +58599,16 @@
         <v>235</v>
       </c>
       <c r="B236" t="s">
+        <v>434</v>
+      </c>
+      <c r="C236" t="s">
         <v>435</v>
-      </c>
-      <c r="C236" t="s">
-        <v>436</v>
       </c>
       <c r="D236">
         <v>235374563</v>
       </c>
       <c r="E236" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="F236" t="s">
         <v>138</v>
@@ -58797,16 +58794,16 @@
         <v>82</v>
       </c>
       <c r="BO236" t="s">
+        <v>664</v>
+      </c>
+      <c r="BP236" t="s">
+        <v>82</v>
+      </c>
+      <c r="BQ236" t="s">
+        <v>341</v>
+      </c>
+      <c r="BR236" t="s">
         <v>665</v>
-      </c>
-      <c r="BP236" t="s">
-        <v>82</v>
-      </c>
-      <c r="BQ236" t="s">
-        <v>342</v>
-      </c>
-      <c r="BR236" t="s">
-        <v>666</v>
       </c>
       <c r="BS236">
         <v>NaN</v>
@@ -58838,16 +58835,16 @@
         <v>236</v>
       </c>
       <c r="B237" t="s">
+        <v>434</v>
+      </c>
+      <c r="C237" t="s">
         <v>435</v>
-      </c>
-      <c r="C237" t="s">
-        <v>436</v>
       </c>
       <c r="D237">
         <v>235410837</v>
       </c>
       <c r="E237" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="F237" t="s">
         <v>138</v>
@@ -59033,16 +59030,16 @@
         <v>82</v>
       </c>
       <c r="BO237" t="s">
+        <v>667</v>
+      </c>
+      <c r="BP237" t="s">
+        <v>82</v>
+      </c>
+      <c r="BQ237" t="s">
+        <v>341</v>
+      </c>
+      <c r="BR237" t="s">
         <v>668</v>
-      </c>
-      <c r="BP237" t="s">
-        <v>82</v>
-      </c>
-      <c r="BQ237" t="s">
-        <v>342</v>
-      </c>
-      <c r="BR237" t="s">
-        <v>669</v>
       </c>
       <c r="BS237">
         <v>NaN</v>
@@ -59074,16 +59071,16 @@
         <v>237</v>
       </c>
       <c r="B238" t="s">
+        <v>434</v>
+      </c>
+      <c r="C238" t="s">
         <v>435</v>
-      </c>
-      <c r="C238" t="s">
-        <v>436</v>
       </c>
       <c r="D238">
         <v>235757828</v>
       </c>
       <c r="E238" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="F238" t="s">
         <v>178</v>
@@ -59260,7 +59257,7 @@
         <v>0</v>
       </c>
       <c r="BL238" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="BM238">
         <v>263411567</v>
@@ -59269,22 +59266,22 @@
         <v>82</v>
       </c>
       <c r="BO238" t="s">
+        <v>671</v>
+      </c>
+      <c r="BP238" t="s">
+        <v>82</v>
+      </c>
+      <c r="BQ238" t="s">
+        <v>333</v>
+      </c>
+      <c r="BR238" t="s">
         <v>672</v>
-      </c>
-      <c r="BP238" t="s">
-        <v>82</v>
-      </c>
-      <c r="BQ238" t="s">
-        <v>334</v>
-      </c>
-      <c r="BR238" t="s">
-        <v>673</v>
       </c>
       <c r="BS238">
         <v>NaN</v>
       </c>
       <c r="BT238" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="BU238" t="s">
         <v>82</v>
@@ -59310,16 +59307,16 @@
         <v>238</v>
       </c>
       <c r="B239" t="s">
+        <v>434</v>
+      </c>
+      <c r="C239" t="s">
         <v>435</v>
-      </c>
-      <c r="C239" t="s">
-        <v>436</v>
       </c>
       <c r="D239">
         <v>235362405</v>
       </c>
       <c r="E239" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="F239" t="s">
         <v>106</v>
@@ -59505,22 +59502,22 @@
         <v>82</v>
       </c>
       <c r="BO239" t="s">
+        <v>675</v>
+      </c>
+      <c r="BP239" t="s">
+        <v>82</v>
+      </c>
+      <c r="BQ239" t="s">
+        <v>341</v>
+      </c>
+      <c r="BR239" t="s">
         <v>676</v>
-      </c>
-      <c r="BP239" t="s">
-        <v>82</v>
-      </c>
-      <c r="BQ239" t="s">
-        <v>342</v>
-      </c>
-      <c r="BR239" t="s">
-        <v>677</v>
       </c>
       <c r="BS239">
         <v>NaN</v>
       </c>
       <c r="BT239" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="BU239" t="s">
         <v>82</v>
@@ -59546,16 +59543,16 @@
         <v>239</v>
       </c>
       <c r="B240" t="s">
+        <v>434</v>
+      </c>
+      <c r="C240" t="s">
         <v>435</v>
-      </c>
-      <c r="C240" t="s">
-        <v>436</v>
       </c>
       <c r="D240">
         <v>235371362</v>
       </c>
       <c r="E240" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="F240" t="s">
         <v>138</v>
@@ -59732,7 +59729,7 @@
         <v>0</v>
       </c>
       <c r="BL240" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="BM240">
         <v>226917506</v>
@@ -59741,7 +59738,7 @@
         <v>82</v>
       </c>
       <c r="BO240" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="BP240" t="s">
         <v>82</v>
@@ -59750,7 +59747,7 @@
         <v>175</v>
       </c>
       <c r="BR240" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="BS240">
         <v>NaN</v>
@@ -59782,16 +59779,16 @@
         <v>240</v>
       </c>
       <c r="B241" t="s">
+        <v>434</v>
+      </c>
+      <c r="C241" t="s">
         <v>435</v>
-      </c>
-      <c r="C241" t="s">
-        <v>436</v>
       </c>
       <c r="D241">
         <v>235442347</v>
       </c>
       <c r="E241" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="F241" t="s">
         <v>119</v>
@@ -59968,7 +59965,7 @@
         <v>0</v>
       </c>
       <c r="BL241" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="BM241">
         <v>96196071</v>
@@ -59977,16 +59974,16 @@
         <v>82</v>
       </c>
       <c r="BO241" t="s">
+        <v>683</v>
+      </c>
+      <c r="BP241" t="s">
+        <v>82</v>
+      </c>
+      <c r="BQ241" t="s">
+        <v>341</v>
+      </c>
+      <c r="BR241" t="s">
         <v>684</v>
-      </c>
-      <c r="BP241" t="s">
-        <v>82</v>
-      </c>
-      <c r="BQ241" t="s">
-        <v>342</v>
-      </c>
-      <c r="BR241" t="s">
-        <v>685</v>
       </c>
       <c r="BS241">
         <v>NaN</v>
@@ -60018,16 +60015,16 @@
         <v>241</v>
       </c>
       <c r="B242" t="s">
+        <v>434</v>
+      </c>
+      <c r="C242" t="s">
         <v>435</v>
-      </c>
-      <c r="C242" t="s">
-        <v>436</v>
       </c>
       <c r="D242">
         <v>235370647</v>
       </c>
       <c r="E242" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="F242" t="s">
         <v>178</v>
@@ -60213,7 +60210,7 @@
         <v>82</v>
       </c>
       <c r="BO242" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="BP242" t="s">
         <v>82</v>
@@ -60222,13 +60219,13 @@
         <v>157</v>
       </c>
       <c r="BR242" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="BS242">
         <v>NaN</v>
       </c>
       <c r="BT242" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="BU242" t="s">
         <v>82</v>
@@ -60254,16 +60251,16 @@
         <v>242</v>
       </c>
       <c r="B243" t="s">
+        <v>434</v>
+      </c>
+      <c r="C243" t="s">
         <v>435</v>
-      </c>
-      <c r="C243" t="s">
-        <v>436</v>
       </c>
       <c r="D243">
         <v>235431933</v>
       </c>
       <c r="E243" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="F243" t="s">
         <v>138</v>
@@ -60440,7 +60437,7 @@
         <v>0</v>
       </c>
       <c r="BL243" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="BM243">
         <v>228861663</v>
@@ -60449,7 +60446,7 @@
         <v>82</v>
       </c>
       <c r="BO243" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="BP243" t="s">
         <v>82</v>
@@ -60458,7 +60455,7 @@
         <v>175</v>
       </c>
       <c r="BR243" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="BS243">
         <v>NaN</v>
@@ -60490,16 +60487,16 @@
         <v>243</v>
       </c>
       <c r="B244" t="s">
+        <v>434</v>
+      </c>
+      <c r="C244" t="s">
         <v>435</v>
-      </c>
-      <c r="C244" t="s">
-        <v>436</v>
       </c>
       <c r="D244">
         <v>235717460</v>
       </c>
       <c r="E244" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="F244" t="s">
         <v>94</v>
@@ -60726,22 +60723,22 @@
         <v>244</v>
       </c>
       <c r="B245" t="s">
+        <v>434</v>
+      </c>
+      <c r="C245" t="s">
         <v>435</v>
-      </c>
-      <c r="C245" t="s">
-        <v>436</v>
       </c>
       <c r="D245">
         <v>235730005</v>
       </c>
       <c r="E245" t="s">
+        <v>693</v>
+      </c>
+      <c r="F245" t="s">
         <v>694</v>
       </c>
-      <c r="F245" t="s">
+      <c r="G245" t="s">
         <v>695</v>
-      </c>
-      <c r="G245" t="s">
-        <v>696</v>
       </c>
       <c r="H245">
         <v>8908906</v>
@@ -60921,22 +60918,22 @@
         <v>82</v>
       </c>
       <c r="BO245" t="s">
+        <v>696</v>
+      </c>
+      <c r="BP245" t="s">
+        <v>82</v>
+      </c>
+      <c r="BQ245" t="s">
+        <v>333</v>
+      </c>
+      <c r="BR245" t="s">
         <v>697</v>
-      </c>
-      <c r="BP245" t="s">
-        <v>82</v>
-      </c>
-      <c r="BQ245" t="s">
-        <v>334</v>
-      </c>
-      <c r="BR245" t="s">
-        <v>698</v>
       </c>
       <c r="BS245">
         <v>NaN</v>
       </c>
       <c r="BT245" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="BU245" t="s">
         <v>82</v>
@@ -60962,16 +60959,16 @@
         <v>245</v>
       </c>
       <c r="B246" t="s">
+        <v>434</v>
+      </c>
+      <c r="C246" t="s">
         <v>435</v>
-      </c>
-      <c r="C246" t="s">
-        <v>436</v>
       </c>
       <c r="D246">
         <v>235447073</v>
       </c>
       <c r="E246" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="F246" t="s">
         <v>119</v>
@@ -61118,13 +61115,13 @@
         <v>10</v>
       </c>
       <c r="BB246" t="s">
+        <v>700</v>
+      </c>
+      <c r="BC246" t="s">
+        <v>82</v>
+      </c>
+      <c r="BD246" t="s">
         <v>701</v>
-      </c>
-      <c r="BC246" t="s">
-        <v>82</v>
-      </c>
-      <c r="BD246" t="s">
-        <v>702</v>
       </c>
       <c r="BE246" t="s">
         <v>82</v>
@@ -61157,25 +61154,25 @@
         <v>82</v>
       </c>
       <c r="BO246" t="s">
+        <v>702</v>
+      </c>
+      <c r="BP246" t="s">
+        <v>82</v>
+      </c>
+      <c r="BQ246" t="s">
+        <v>485</v>
+      </c>
+      <c r="BR246" t="s">
         <v>703</v>
-      </c>
-      <c r="BP246" t="s">
-        <v>82</v>
-      </c>
-      <c r="BQ246" t="s">
-        <v>486</v>
-      </c>
-      <c r="BR246" t="s">
-        <v>704</v>
       </c>
       <c r="BS246">
         <v>NaN</v>
       </c>
       <c r="BT246" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="BU246" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="BV246">
         <v>0</v>
@@ -61198,16 +61195,16 @@
         <v>246</v>
       </c>
       <c r="B247" t="s">
+        <v>434</v>
+      </c>
+      <c r="C247" t="s">
         <v>435</v>
-      </c>
-      <c r="C247" t="s">
-        <v>436</v>
       </c>
       <c r="D247">
         <v>235726408</v>
       </c>
       <c r="E247" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="F247" t="s">
         <v>94</v>
@@ -61434,16 +61431,16 @@
         <v>247</v>
       </c>
       <c r="B248" t="s">
+        <v>434</v>
+      </c>
+      <c r="C248" t="s">
         <v>435</v>
-      </c>
-      <c r="C248" t="s">
-        <v>436</v>
       </c>
       <c r="D248">
         <v>235371877</v>
       </c>
       <c r="E248" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="F248" t="s">
         <v>169</v>
@@ -61629,22 +61626,22 @@
         <v>82</v>
       </c>
       <c r="BO248" t="s">
+        <v>707</v>
+      </c>
+      <c r="BP248" t="s">
+        <v>82</v>
+      </c>
+      <c r="BQ248" t="s">
+        <v>485</v>
+      </c>
+      <c r="BR248" t="s">
         <v>708</v>
-      </c>
-      <c r="BP248" t="s">
-        <v>82</v>
-      </c>
-      <c r="BQ248" t="s">
-        <v>486</v>
-      </c>
-      <c r="BR248" t="s">
-        <v>709</v>
       </c>
       <c r="BS248">
         <v>NaN</v>
       </c>
       <c r="BT248" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="BU248" t="s">
         <v>82</v>
@@ -61670,22 +61667,22 @@
         <v>248</v>
       </c>
       <c r="B249" t="s">
+        <v>434</v>
+      </c>
+      <c r="C249" t="s">
         <v>435</v>
-      </c>
-      <c r="C249" t="s">
-        <v>436</v>
       </c>
       <c r="D249">
         <v>235388782</v>
       </c>
       <c r="E249" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="F249" t="s">
+        <v>297</v>
+      </c>
+      <c r="G249" t="s">
         <v>298</v>
-      </c>
-      <c r="G249" t="s">
-        <v>299</v>
       </c>
       <c r="H249">
         <v>8908959</v>
@@ -61865,7 +61862,7 @@
         <v>82</v>
       </c>
       <c r="BO249" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="BP249" t="s">
         <v>82</v>
@@ -61874,13 +61871,13 @@
         <v>183</v>
       </c>
       <c r="BR249" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="BS249">
         <v>NaN</v>
       </c>
       <c r="BT249" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="BU249" t="s">
         <v>82</v>
@@ -61906,16 +61903,16 @@
         <v>249</v>
       </c>
       <c r="B250" t="s">
+        <v>434</v>
+      </c>
+      <c r="C250" t="s">
         <v>435</v>
-      </c>
-      <c r="C250" t="s">
-        <v>436</v>
       </c>
       <c r="D250">
         <v>235776258</v>
       </c>
       <c r="E250" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="F250" t="s">
         <v>138</v>
@@ -62092,7 +62089,7 @@
         <v>0</v>
       </c>
       <c r="BL250" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="BM250">
         <v>263406065</v>
@@ -62101,22 +62098,22 @@
         <v>82</v>
       </c>
       <c r="BO250" t="s">
+        <v>716</v>
+      </c>
+      <c r="BP250" t="s">
+        <v>82</v>
+      </c>
+      <c r="BQ250" t="s">
+        <v>485</v>
+      </c>
+      <c r="BR250" t="s">
         <v>717</v>
-      </c>
-      <c r="BP250" t="s">
-        <v>82</v>
-      </c>
-      <c r="BQ250" t="s">
-        <v>486</v>
-      </c>
-      <c r="BR250" t="s">
-        <v>718</v>
       </c>
       <c r="BS250">
         <v>NaN</v>
       </c>
       <c r="BT250" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="BU250" t="s">
         <v>82</v>
@@ -62142,16 +62139,16 @@
         <v>250</v>
       </c>
       <c r="B251" t="s">
+        <v>434</v>
+      </c>
+      <c r="C251" t="s">
         <v>435</v>
-      </c>
-      <c r="C251" t="s">
-        <v>436</v>
       </c>
       <c r="D251">
         <v>235364666</v>
       </c>
       <c r="E251" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="F251" t="s">
         <v>138</v>
@@ -62378,16 +62375,16 @@
         <v>251</v>
       </c>
       <c r="B252" t="s">
+        <v>434</v>
+      </c>
+      <c r="C252" t="s">
         <v>435</v>
-      </c>
-      <c r="C252" t="s">
-        <v>436</v>
       </c>
       <c r="D252">
         <v>235760425</v>
       </c>
       <c r="E252" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="F252" t="s">
         <v>94</v>
@@ -62423,7 +62420,7 @@
         <v>3</v>
       </c>
       <c r="Q252" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="R252">
         <v>12</v>
@@ -62564,7 +62561,7 @@
         <v>0</v>
       </c>
       <c r="BL252" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="BM252">
         <v>0</v>
@@ -62588,7 +62585,7 @@
         <v>NaN</v>
       </c>
       <c r="BT252" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="BU252" t="s">
         <v>82</v>
@@ -62614,22 +62611,22 @@
         <v>252</v>
       </c>
       <c r="B253" t="s">
+        <v>434</v>
+      </c>
+      <c r="C253" t="s">
         <v>435</v>
-      </c>
-      <c r="C253" t="s">
-        <v>436</v>
       </c>
       <c r="D253">
         <v>235879695</v>
       </c>
       <c r="E253" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="F253" t="s">
+        <v>292</v>
+      </c>
+      <c r="G253" t="s">
         <v>293</v>
-      </c>
-      <c r="G253" t="s">
-        <v>294</v>
       </c>
       <c r="H253">
         <v>8908924</v>
@@ -62809,7 +62806,7 @@
         <v>82</v>
       </c>
       <c r="BO253" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="BP253" t="s">
         <v>82</v>
@@ -62818,7 +62815,7 @@
         <v>130</v>
       </c>
       <c r="BR253" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="BS253">
         <v>NaN</v>
@@ -62850,16 +62847,16 @@
         <v>253</v>
       </c>
       <c r="B254" t="s">
+        <v>434</v>
+      </c>
+      <c r="C254" t="s">
         <v>435</v>
-      </c>
-      <c r="C254" t="s">
-        <v>436</v>
       </c>
       <c r="D254">
         <v>235366427</v>
       </c>
       <c r="E254" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="F254" t="s">
         <v>178</v>
@@ -63045,7 +63042,7 @@
         <v>82</v>
       </c>
       <c r="BO254" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="BP254" t="s">
         <v>82</v>
@@ -63054,7 +63051,7 @@
         <v>111</v>
       </c>
       <c r="BR254" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="BS254">
         <v>NaN</v>
@@ -63086,16 +63083,16 @@
         <v>254</v>
       </c>
       <c r="B255" t="s">
+        <v>434</v>
+      </c>
+      <c r="C255" t="s">
         <v>435</v>
-      </c>
-      <c r="C255" t="s">
-        <v>436</v>
       </c>
       <c r="D255">
         <v>235363067</v>
       </c>
       <c r="E255" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="F255" t="s">
         <v>119</v>
@@ -63242,37 +63239,37 @@
         <v>7</v>
       </c>
       <c r="BB255" t="s">
+        <v>729</v>
+      </c>
+      <c r="BC255" t="s">
+        <v>82</v>
+      </c>
+      <c r="BD255" t="s">
         <v>730</v>
       </c>
-      <c r="BC255" t="s">
-        <v>82</v>
-      </c>
-      <c r="BD255" t="s">
+      <c r="BE255" t="s">
+        <v>82</v>
+      </c>
+      <c r="BF255" t="s">
+        <v>82</v>
+      </c>
+      <c r="BG255" t="s">
+        <v>82</v>
+      </c>
+      <c r="BH255">
+        <v>0</v>
+      </c>
+      <c r="BI255" t="s">
+        <v>82</v>
+      </c>
+      <c r="BJ255" t="s">
+        <v>82</v>
+      </c>
+      <c r="BK255">
+        <v>0</v>
+      </c>
+      <c r="BL255" t="s">
         <v>731</v>
-      </c>
-      <c r="BE255" t="s">
-        <v>82</v>
-      </c>
-      <c r="BF255" t="s">
-        <v>82</v>
-      </c>
-      <c r="BG255" t="s">
-        <v>82</v>
-      </c>
-      <c r="BH255">
-        <v>0</v>
-      </c>
-      <c r="BI255" t="s">
-        <v>82</v>
-      </c>
-      <c r="BJ255" t="s">
-        <v>82</v>
-      </c>
-      <c r="BK255">
-        <v>0</v>
-      </c>
-      <c r="BL255" t="s">
-        <v>732</v>
       </c>
       <c r="BM255">
         <v>78864838</v>
@@ -63281,16 +63278,16 @@
         <v>82</v>
       </c>
       <c r="BO255" t="s">
+        <v>732</v>
+      </c>
+      <c r="BP255" t="s">
+        <v>82</v>
+      </c>
+      <c r="BQ255" t="s">
+        <v>476</v>
+      </c>
+      <c r="BR255" t="s">
         <v>733</v>
-      </c>
-      <c r="BP255" t="s">
-        <v>82</v>
-      </c>
-      <c r="BQ255" t="s">
-        <v>477</v>
-      </c>
-      <c r="BR255" t="s">
-        <v>734</v>
       </c>
       <c r="BS255">
         <v>NaN</v>
@@ -63299,7 +63296,7 @@
         <v>82</v>
       </c>
       <c r="BU255" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="BV255">
         <v>0</v>
@@ -63322,16 +63319,16 @@
         <v>255</v>
       </c>
       <c r="B256" t="s">
+        <v>434</v>
+      </c>
+      <c r="C256" t="s">
         <v>435</v>
-      </c>
-      <c r="C256" t="s">
-        <v>436</v>
       </c>
       <c r="D256">
         <v>235693206</v>
       </c>
       <c r="E256" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="F256" t="s">
         <v>106</v>
@@ -63508,7 +63505,7 @@
         <v>0</v>
       </c>
       <c r="BL256" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="BM256">
         <v>255494109</v>
@@ -63517,7 +63514,7 @@
         <v>82</v>
       </c>
       <c r="BO256" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="BP256" t="s">
         <v>82</v>
@@ -63526,7 +63523,7 @@
         <v>229</v>
       </c>
       <c r="BR256" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="BS256">
         <v>NaN</v>
@@ -63558,22 +63555,22 @@
         <v>256</v>
       </c>
       <c r="B257" t="s">
+        <v>434</v>
+      </c>
+      <c r="C257" t="s">
         <v>435</v>
-      </c>
-      <c r="C257" t="s">
-        <v>436</v>
       </c>
       <c r="D257">
         <v>235693717</v>
       </c>
       <c r="E257" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="F257" t="s">
+        <v>292</v>
+      </c>
+      <c r="G257" t="s">
         <v>293</v>
-      </c>
-      <c r="G257" t="s">
-        <v>294</v>
       </c>
       <c r="H257">
         <v>8908924</v>
@@ -63603,7 +63600,7 @@
         <v>1</v>
       </c>
       <c r="Q257" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="R257">
         <v>12</v>
@@ -63753,16 +63750,16 @@
         <v>82</v>
       </c>
       <c r="BO257" t="s">
+        <v>740</v>
+      </c>
+      <c r="BP257" t="s">
+        <v>82</v>
+      </c>
+      <c r="BQ257" t="s">
+        <v>254</v>
+      </c>
+      <c r="BR257" t="s">
         <v>741</v>
-      </c>
-      <c r="BP257" t="s">
-        <v>82</v>
-      </c>
-      <c r="BQ257" t="s">
-        <v>255</v>
-      </c>
-      <c r="BR257" t="s">
-        <v>742</v>
       </c>
       <c r="BS257">
         <v>NaN</v>
@@ -63794,16 +63791,16 @@
         <v>257</v>
       </c>
       <c r="B258" t="s">
+        <v>434</v>
+      </c>
+      <c r="C258" t="s">
         <v>435</v>
-      </c>
-      <c r="C258" t="s">
-        <v>436</v>
       </c>
       <c r="D258">
         <v>235706476</v>
       </c>
       <c r="E258" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="F258" t="s">
         <v>138</v>
@@ -64004,7 +64001,7 @@
         <v>NaN</v>
       </c>
       <c r="BT258" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="BU258" t="s">
         <v>82</v>
@@ -64030,22 +64027,22 @@
         <v>258</v>
       </c>
       <c r="B259" t="s">
+        <v>434</v>
+      </c>
+      <c r="C259" t="s">
         <v>435</v>
-      </c>
-      <c r="C259" t="s">
-        <v>436</v>
       </c>
       <c r="D259">
         <v>235715035</v>
       </c>
       <c r="E259" t="s">
+        <v>743</v>
+      </c>
+      <c r="F259" t="s">
         <v>744</v>
       </c>
-      <c r="F259" t="s">
+      <c r="G259" t="s">
         <v>745</v>
-      </c>
-      <c r="G259" t="s">
-        <v>746</v>
       </c>
       <c r="H259">
         <v>8908976</v>
@@ -64075,7 +64072,7 @@
         <v>4</v>
       </c>
       <c r="Q259" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="R259">
         <v>10</v>
@@ -64216,7 +64213,7 @@
         <v>0</v>
       </c>
       <c r="BL259" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="BM259">
         <v>263043305</v>
@@ -64225,7 +64222,7 @@
         <v>82</v>
       </c>
       <c r="BO259" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="BP259" t="s">
         <v>82</v>
@@ -64234,13 +64231,13 @@
         <v>216</v>
       </c>
       <c r="BR259" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="BS259">
         <v>NaN</v>
       </c>
       <c r="BT259" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="BU259" t="s">
         <v>82</v>
@@ -64266,16 +64263,16 @@
         <v>259</v>
       </c>
       <c r="B260" t="s">
+        <v>434</v>
+      </c>
+      <c r="C260" t="s">
         <v>435</v>
-      </c>
-      <c r="C260" t="s">
-        <v>436</v>
       </c>
       <c r="D260">
         <v>235698279</v>
       </c>
       <c r="E260" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="F260" t="s">
         <v>178</v>
@@ -64461,16 +64458,16 @@
         <v>82</v>
       </c>
       <c r="BO260" t="s">
+        <v>751</v>
+      </c>
+      <c r="BP260" t="s">
+        <v>82</v>
+      </c>
+      <c r="BQ260" t="s">
+        <v>590</v>
+      </c>
+      <c r="BR260" t="s">
         <v>752</v>
-      </c>
-      <c r="BP260" t="s">
-        <v>82</v>
-      </c>
-      <c r="BQ260" t="s">
-        <v>591</v>
-      </c>
-      <c r="BR260" t="s">
-        <v>753</v>
       </c>
       <c r="BS260">
         <v>NaN</v>
@@ -64502,16 +64499,16 @@
         <v>260</v>
       </c>
       <c r="B261" t="s">
+        <v>434</v>
+      </c>
+      <c r="C261" t="s">
         <v>435</v>
-      </c>
-      <c r="C261" t="s">
-        <v>436</v>
       </c>
       <c r="D261">
         <v>235716018</v>
       </c>
       <c r="E261" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="F261" t="s">
         <v>119</v>
@@ -64547,7 +64544,7 @@
         <v>1</v>
       </c>
       <c r="Q261" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="R261">
         <v>12</v>
@@ -64712,7 +64709,7 @@
         <v>0</v>
       </c>
       <c r="BT261" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="BU261" t="s">
         <v>82</v>
@@ -64738,16 +64735,16 @@
         <v>261</v>
       </c>
       <c r="B262" t="s">
+        <v>434</v>
+      </c>
+      <c r="C262" t="s">
         <v>435</v>
-      </c>
-      <c r="C262" t="s">
-        <v>436</v>
       </c>
       <c r="D262">
         <v>235693218</v>
       </c>
       <c r="E262" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="F262" t="s">
         <v>163</v>
@@ -64933,7 +64930,7 @@
         <v>82</v>
       </c>
       <c r="BO262" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="BP262" t="s">
         <v>82</v>
@@ -64942,7 +64939,7 @@
         <v>216</v>
       </c>
       <c r="BR262" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="BS262">
         <v>NaN</v>
@@ -64974,16 +64971,16 @@
         <v>262</v>
       </c>
       <c r="B263" t="s">
+        <v>434</v>
+      </c>
+      <c r="C263" t="s">
         <v>435</v>
-      </c>
-      <c r="C263" t="s">
-        <v>436</v>
       </c>
       <c r="D263">
         <v>235698227</v>
       </c>
       <c r="E263" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="F263" t="s">
         <v>138</v>
@@ -65169,22 +65166,22 @@
         <v>82</v>
       </c>
       <c r="BO263" t="s">
+        <v>758</v>
+      </c>
+      <c r="BP263" t="s">
+        <v>82</v>
+      </c>
+      <c r="BQ263" t="s">
+        <v>354</v>
+      </c>
+      <c r="BR263" t="s">
         <v>759</v>
-      </c>
-      <c r="BP263" t="s">
-        <v>82</v>
-      </c>
-      <c r="BQ263" t="s">
-        <v>355</v>
-      </c>
-      <c r="BR263" t="s">
-        <v>760</v>
       </c>
       <c r="BS263">
         <v>NaN</v>
       </c>
       <c r="BT263" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="BU263" t="s">
         <v>82</v>
@@ -65210,16 +65207,16 @@
         <v>263</v>
       </c>
       <c r="B264" t="s">
+        <v>434</v>
+      </c>
+      <c r="C264" t="s">
         <v>435</v>
-      </c>
-      <c r="C264" t="s">
-        <v>436</v>
       </c>
       <c r="D264">
         <v>235391164</v>
       </c>
       <c r="E264" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="F264" t="s">
         <v>106</v>
@@ -65405,22 +65402,22 @@
         <v>82</v>
       </c>
       <c r="BO264" t="s">
+        <v>761</v>
+      </c>
+      <c r="BP264" t="s">
+        <v>82</v>
+      </c>
+      <c r="BQ264" t="s">
+        <v>485</v>
+      </c>
+      <c r="BR264" t="s">
         <v>762</v>
-      </c>
-      <c r="BP264" t="s">
-        <v>82</v>
-      </c>
-      <c r="BQ264" t="s">
-        <v>486</v>
-      </c>
-      <c r="BR264" t="s">
-        <v>763</v>
       </c>
       <c r="BS264">
         <v>NaN</v>
       </c>
       <c r="BT264" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="BU264" t="s">
         <v>82</v>
@@ -65446,16 +65443,16 @@
         <v>264</v>
       </c>
       <c r="B265" t="s">
+        <v>434</v>
+      </c>
+      <c r="C265" t="s">
         <v>435</v>
-      </c>
-      <c r="C265" t="s">
-        <v>436</v>
       </c>
       <c r="D265">
         <v>235661476</v>
       </c>
       <c r="E265" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="F265" t="s">
         <v>94</v>
@@ -65641,7 +65638,7 @@
         <v>82</v>
       </c>
       <c r="BO265" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="BP265" t="s">
         <v>82</v>
@@ -65650,13 +65647,13 @@
         <v>241</v>
       </c>
       <c r="BR265" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="BS265">
         <v>NaN</v>
       </c>
       <c r="BT265" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="BU265" t="s">
         <v>82</v>
@@ -65682,16 +65679,16 @@
         <v>265</v>
       </c>
       <c r="B266" t="s">
+        <v>434</v>
+      </c>
+      <c r="C266" t="s">
         <v>435</v>
-      </c>
-      <c r="C266" t="s">
-        <v>436</v>
       </c>
       <c r="D266">
         <v>235366525</v>
       </c>
       <c r="E266" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="F266" t="s">
         <v>81</v>
@@ -65868,7 +65865,7 @@
         <v>0</v>
       </c>
       <c r="BL266" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="BM266">
         <v>263043475</v>
@@ -65877,16 +65874,16 @@
         <v>82</v>
       </c>
       <c r="BO266" t="s">
+        <v>768</v>
+      </c>
+      <c r="BP266" t="s">
+        <v>82</v>
+      </c>
+      <c r="BQ266" t="s">
+        <v>476</v>
+      </c>
+      <c r="BR266" t="s">
         <v>769</v>
-      </c>
-      <c r="BP266" t="s">
-        <v>82</v>
-      </c>
-      <c r="BQ266" t="s">
-        <v>477</v>
-      </c>
-      <c r="BR266" t="s">
-        <v>770</v>
       </c>
       <c r="BS266">
         <v>NaN</v>
@@ -65918,16 +65915,16 @@
         <v>266</v>
       </c>
       <c r="B267" t="s">
+        <v>434</v>
+      </c>
+      <c r="C267" t="s">
         <v>435</v>
-      </c>
-      <c r="C267" t="s">
-        <v>436</v>
       </c>
       <c r="D267">
         <v>235504172</v>
       </c>
       <c r="E267" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="F267" t="s">
         <v>163</v>
@@ -65963,7 +65960,7 @@
         <v>3</v>
       </c>
       <c r="Q267" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="R267">
         <v>5</v>
@@ -66113,7 +66110,7 @@
         <v>82</v>
       </c>
       <c r="BO267" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="BP267" t="s">
         <v>82</v>
@@ -66122,13 +66119,13 @@
         <v>183</v>
       </c>
       <c r="BR267" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="BS267">
         <v>NaN</v>
       </c>
       <c r="BT267" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="BU267" t="s">
         <v>82</v>
@@ -66154,22 +66151,22 @@
         <v>267</v>
       </c>
       <c r="B268" t="s">
+        <v>434</v>
+      </c>
+      <c r="C268" t="s">
         <v>435</v>
-      </c>
-      <c r="C268" t="s">
-        <v>436</v>
       </c>
       <c r="D268">
         <v>235380996</v>
       </c>
       <c r="E268" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="F268" t="s">
+        <v>384</v>
+      </c>
+      <c r="G268" t="s">
         <v>385</v>
-      </c>
-      <c r="G268" t="s">
-        <v>386</v>
       </c>
       <c r="H268">
         <v>8909361</v>
@@ -66340,7 +66337,7 @@
         <v>0</v>
       </c>
       <c r="BL268" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="BM268">
         <v>0</v>
@@ -66364,7 +66361,7 @@
         <v>NaN</v>
       </c>
       <c r="BT268" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="BU268" t="s">
         <v>82</v>
@@ -66390,16 +66387,16 @@
         <v>268</v>
       </c>
       <c r="B269" t="s">
+        <v>434</v>
+      </c>
+      <c r="C269" t="s">
         <v>435</v>
-      </c>
-      <c r="C269" t="s">
-        <v>436</v>
       </c>
       <c r="D269">
         <v>235438683</v>
       </c>
       <c r="E269" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="F269" t="s">
         <v>138</v>
@@ -66576,7 +66573,7 @@
         <v>0</v>
       </c>
       <c r="BL269" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="BM269">
         <v>0</v>
@@ -66600,7 +66597,7 @@
         <v>NaN</v>
       </c>
       <c r="BT269" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="BU269" t="s">
         <v>82</v>
@@ -66626,22 +66623,22 @@
         <v>269</v>
       </c>
       <c r="B270" t="s">
+        <v>434</v>
+      </c>
+      <c r="C270" t="s">
         <v>435</v>
-      </c>
-      <c r="C270" t="s">
-        <v>436</v>
       </c>
       <c r="D270">
         <v>235810631</v>
       </c>
       <c r="E270" t="s">
+        <v>779</v>
+      </c>
+      <c r="F270" t="s">
         <v>780</v>
       </c>
-      <c r="F270" t="s">
+      <c r="G270" t="s">
         <v>781</v>
-      </c>
-      <c r="G270" t="s">
-        <v>782</v>
       </c>
       <c r="H270">
         <v>8909085</v>
@@ -66836,7 +66833,7 @@
         <v>NaN</v>
       </c>
       <c r="BT270" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
       <c r="BU270" t="s">
         <v>82</v>
@@ -66862,22 +66859,22 @@
         <v>270</v>
       </c>
       <c r="B271" t="s">
+        <v>434</v>
+      </c>
+      <c r="C271" t="s">
         <v>435</v>
-      </c>
-      <c r="C271" t="s">
-        <v>436</v>
       </c>
       <c r="D271">
         <v>235718919</v>
       </c>
       <c r="E271" t="s">
+        <v>783</v>
+      </c>
+      <c r="F271" t="s">
         <v>784</v>
       </c>
-      <c r="F271" t="s">
+      <c r="G271" t="s">
         <v>785</v>
-      </c>
-      <c r="G271" t="s">
-        <v>786</v>
       </c>
       <c r="H271">
         <v>8911001</v>
@@ -67057,7 +67054,7 @@
         <v>82</v>
       </c>
       <c r="BO271" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="BP271" t="s">
         <v>82</v>
@@ -67066,13 +67063,13 @@
         <v>157</v>
       </c>
       <c r="BR271" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="BS271">
         <v>NaN</v>
       </c>
       <c r="BT271" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="BU271" t="s">
         <v>82</v>
@@ -67098,16 +67095,16 @@
         <v>271</v>
       </c>
       <c r="B272" t="s">
+        <v>434</v>
+      </c>
+      <c r="C272" t="s">
         <v>435</v>
-      </c>
-      <c r="C272" t="s">
-        <v>436</v>
       </c>
       <c r="D272">
         <v>235379542</v>
       </c>
       <c r="E272" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="F272" t="s">
         <v>138</v>
@@ -67293,7 +67290,7 @@
         <v>82</v>
       </c>
       <c r="BO272" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="BP272" t="s">
         <v>82</v>
@@ -67302,13 +67299,13 @@
         <v>130</v>
       </c>
       <c r="BR272" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="BS272">
         <v>NaN</v>
       </c>
       <c r="BT272" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="BU272" t="s">
         <v>82</v>
@@ -67334,16 +67331,16 @@
         <v>272</v>
       </c>
       <c r="B273" t="s">
+        <v>434</v>
+      </c>
+      <c r="C273" t="s">
         <v>435</v>
-      </c>
-      <c r="C273" t="s">
-        <v>436</v>
       </c>
       <c r="D273">
         <v>235722665</v>
       </c>
       <c r="E273" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="F273" t="s">
         <v>81</v>
@@ -67570,16 +67567,16 @@
         <v>273</v>
       </c>
       <c r="B274" t="s">
+        <v>434</v>
+      </c>
+      <c r="C274" t="s">
         <v>435</v>
-      </c>
-      <c r="C274" t="s">
-        <v>436</v>
       </c>
       <c r="D274">
         <v>235755508</v>
       </c>
       <c r="E274" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
       <c r="F274" t="s">
         <v>106</v>
@@ -67756,7 +67753,7 @@
         <v>0</v>
       </c>
       <c r="BL274" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
       <c r="BM274">
         <v>28773328</v>
@@ -67765,22 +67762,22 @@
         <v>82</v>
       </c>
       <c r="BO274" t="s">
+        <v>795</v>
+      </c>
+      <c r="BP274" t="s">
+        <v>82</v>
+      </c>
+      <c r="BQ274" t="s">
+        <v>263</v>
+      </c>
+      <c r="BR274" t="s">
         <v>796</v>
-      </c>
-      <c r="BP274" t="s">
-        <v>82</v>
-      </c>
-      <c r="BQ274" t="s">
-        <v>264</v>
-      </c>
-      <c r="BR274" t="s">
-        <v>797</v>
       </c>
       <c r="BS274">
         <v>NaN</v>
       </c>
       <c r="BT274" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="BU274" t="s">
         <v>82</v>
@@ -67806,16 +67803,16 @@
         <v>274</v>
       </c>
       <c r="B275" t="s">
+        <v>434</v>
+      </c>
+      <c r="C275" t="s">
         <v>435</v>
-      </c>
-      <c r="C275" t="s">
-        <v>436</v>
       </c>
       <c r="D275">
         <v>235693830</v>
       </c>
       <c r="E275" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="F275" t="s">
         <v>106</v>
@@ -67992,7 +67989,7 @@
         <v>0</v>
       </c>
       <c r="BL275" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="BM275">
         <v>212471909</v>
@@ -68001,22 +67998,22 @@
         <v>82</v>
       </c>
       <c r="BO275" t="s">
+        <v>799</v>
+      </c>
+      <c r="BP275" t="s">
+        <v>82</v>
+      </c>
+      <c r="BQ275" t="s">
+        <v>354</v>
+      </c>
+      <c r="BR275" t="s">
         <v>800</v>
-      </c>
-      <c r="BP275" t="s">
-        <v>82</v>
-      </c>
-      <c r="BQ275" t="s">
-        <v>355</v>
-      </c>
-      <c r="BR275" t="s">
-        <v>801</v>
       </c>
       <c r="BS275">
         <v>NaN</v>
       </c>
       <c r="BT275" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="BU275" t="s">
         <v>82</v>
@@ -68042,16 +68039,16 @@
         <v>275</v>
       </c>
       <c r="B276" t="s">
+        <v>434</v>
+      </c>
+      <c r="C276" t="s">
         <v>435</v>
-      </c>
-      <c r="C276" t="s">
-        <v>436</v>
       </c>
       <c r="D276">
         <v>235452529</v>
       </c>
       <c r="E276" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="F276" t="s">
         <v>138</v>
@@ -68228,7 +68225,7 @@
         <v>0</v>
       </c>
       <c r="BL276" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="BM276">
         <v>0</v>
@@ -68278,16 +68275,16 @@
         <v>276</v>
       </c>
       <c r="B277" t="s">
+        <v>434</v>
+      </c>
+      <c r="C277" t="s">
         <v>435</v>
-      </c>
-      <c r="C277" t="s">
-        <v>436</v>
       </c>
       <c r="D277">
         <v>235380676</v>
       </c>
       <c r="E277" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="F277" t="s">
         <v>169</v>
@@ -68323,7 +68320,7 @@
         <v>1</v>
       </c>
       <c r="Q277" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="R277">
         <v>12</v>
@@ -68464,7 +68461,7 @@
         <v>0</v>
       </c>
       <c r="BL277" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="BM277">
         <v>209086355</v>
@@ -68473,7 +68470,7 @@
         <v>82</v>
       </c>
       <c r="BO277" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="BP277" t="s">
         <v>82</v>
@@ -68482,13 +68479,13 @@
         <v>175</v>
       </c>
       <c r="BR277" t="s">
-        <v>807</v>
+        <v>806</v>
       </c>
       <c r="BS277">
         <v>NaN</v>
       </c>
       <c r="BT277" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="BU277" t="s">
         <v>82</v>
@@ -68514,16 +68511,16 @@
         <v>277</v>
       </c>
       <c r="B278" t="s">
+        <v>434</v>
+      </c>
+      <c r="C278" t="s">
         <v>435</v>
-      </c>
-      <c r="C278" t="s">
-        <v>436</v>
       </c>
       <c r="D278">
         <v>235733953</v>
       </c>
       <c r="E278" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="F278" t="s">
         <v>106</v>
@@ -68709,7 +68706,7 @@
         <v>82</v>
       </c>
       <c r="BO278" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
       <c r="BP278" t="s">
         <v>82</v>
@@ -68718,7 +68715,7 @@
         <v>193</v>
       </c>
       <c r="BR278" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="BS278">
         <v>NaN</v>
@@ -68750,16 +68747,16 @@
         <v>278</v>
       </c>
       <c r="B279" t="s">
+        <v>434</v>
+      </c>
+      <c r="C279" t="s">
         <v>435</v>
-      </c>
-      <c r="C279" t="s">
-        <v>436</v>
       </c>
       <c r="D279">
         <v>235705928</v>
       </c>
       <c r="E279" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="F279" t="s">
         <v>94</v>
@@ -68936,7 +68933,7 @@
         <v>0</v>
       </c>
       <c r="BL279" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="BM279">
         <v>28772082</v>
@@ -68945,22 +68942,22 @@
         <v>82</v>
       </c>
       <c r="BO279" t="s">
+        <v>812</v>
+      </c>
+      <c r="BP279" t="s">
+        <v>82</v>
+      </c>
+      <c r="BQ279" t="s">
+        <v>354</v>
+      </c>
+      <c r="BR279" t="s">
         <v>813</v>
-      </c>
-      <c r="BP279" t="s">
-        <v>82</v>
-      </c>
-      <c r="BQ279" t="s">
-        <v>355</v>
-      </c>
-      <c r="BR279" t="s">
-        <v>814</v>
       </c>
       <c r="BS279">
         <v>NaN</v>
       </c>
       <c r="BT279" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="BU279" t="s">
         <v>82</v>
@@ -68986,16 +68983,16 @@
         <v>279</v>
       </c>
       <c r="B280" t="s">
+        <v>434</v>
+      </c>
+      <c r="C280" t="s">
         <v>435</v>
-      </c>
-      <c r="C280" t="s">
-        <v>436</v>
       </c>
       <c r="D280">
         <v>235728813</v>
       </c>
       <c r="E280" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="F280" t="s">
         <v>94</v>
@@ -69172,7 +69169,7 @@
         <v>0</v>
       </c>
       <c r="BL280" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="BM280">
         <v>25880166</v>
@@ -69181,7 +69178,7 @@
         <v>82</v>
       </c>
       <c r="BO280" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
       <c r="BP280" t="s">
         <v>82</v>
@@ -69190,7 +69187,7 @@
         <v>216</v>
       </c>
       <c r="BR280" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="BS280">
         <v>NaN</v>
@@ -69222,16 +69219,16 @@
         <v>280</v>
       </c>
       <c r="B281" t="s">
+        <v>434</v>
+      </c>
+      <c r="C281" t="s">
         <v>435</v>
-      </c>
-      <c r="C281" t="s">
-        <v>436</v>
       </c>
       <c r="D281">
         <v>235799089</v>
       </c>
       <c r="E281" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="F281" t="s">
         <v>138</v>
@@ -69417,7 +69414,7 @@
         <v>82</v>
       </c>
       <c r="BO281" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="BP281" t="s">
         <v>82</v>
@@ -69426,13 +69423,13 @@
         <v>183</v>
       </c>
       <c r="BR281" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="BS281">
         <v>NaN</v>
       </c>
       <c r="BT281" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="BU281" t="s">
         <v>82</v>
@@ -69458,16 +69455,16 @@
         <v>281</v>
       </c>
       <c r="B282" t="s">
+        <v>434</v>
+      </c>
+      <c r="C282" t="s">
         <v>435</v>
-      </c>
-      <c r="C282" t="s">
-        <v>436</v>
       </c>
       <c r="D282">
         <v>235505276</v>
       </c>
       <c r="E282" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
       <c r="F282" t="s">
         <v>138</v>
@@ -69644,7 +69641,7 @@
         <v>0</v>
       </c>
       <c r="BL282" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="BM282">
         <v>217727205</v>
@@ -69653,22 +69650,22 @@
         <v>82</v>
       </c>
       <c r="BO282" t="s">
+        <v>823</v>
+      </c>
+      <c r="BP282" t="s">
+        <v>82</v>
+      </c>
+      <c r="BQ282" t="s">
+        <v>499</v>
+      </c>
+      <c r="BR282" t="s">
         <v>824</v>
-      </c>
-      <c r="BP282" t="s">
-        <v>82</v>
-      </c>
-      <c r="BQ282" t="s">
-        <v>500</v>
-      </c>
-      <c r="BR282" t="s">
-        <v>825</v>
       </c>
       <c r="BS282">
         <v>NaN</v>
       </c>
       <c r="BT282" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="BU282" t="s">
         <v>82</v>
@@ -69694,16 +69691,16 @@
         <v>282</v>
       </c>
       <c r="B283" t="s">
+        <v>434</v>
+      </c>
+      <c r="C283" t="s">
         <v>435</v>
-      </c>
-      <c r="C283" t="s">
-        <v>436</v>
       </c>
       <c r="D283">
         <v>235719621</v>
       </c>
       <c r="E283" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
       <c r="F283" t="s">
         <v>94</v>
@@ -69889,7 +69886,7 @@
         <v>82</v>
       </c>
       <c r="BO283" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
       <c r="BP283" t="s">
         <v>82</v>
@@ -69898,13 +69895,13 @@
         <v>183</v>
       </c>
       <c r="BR283" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="BS283">
         <v>NaN</v>
       </c>
       <c r="BT283" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="BU283" t="s">
         <v>82</v>
@@ -69930,16 +69927,16 @@
         <v>283</v>
       </c>
       <c r="B284" t="s">
+        <v>434</v>
+      </c>
+      <c r="C284" t="s">
         <v>435</v>
-      </c>
-      <c r="C284" t="s">
-        <v>436</v>
       </c>
       <c r="D284">
         <v>235524873</v>
       </c>
       <c r="E284" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="F284" t="s">
         <v>138</v>
@@ -70125,7 +70122,7 @@
         <v>82</v>
       </c>
       <c r="BO284" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="BP284" t="s">
         <v>82</v>
@@ -70134,7 +70131,7 @@
         <v>241</v>
       </c>
       <c r="BR284" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="BS284">
         <v>NaN</v>
@@ -70166,16 +70163,16 @@
         <v>284</v>
       </c>
       <c r="B285" t="s">
+        <v>434</v>
+      </c>
+      <c r="C285" t="s">
         <v>435</v>
-      </c>
-      <c r="C285" t="s">
-        <v>436</v>
       </c>
       <c r="D285">
         <v>235402378</v>
       </c>
       <c r="E285" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="F285" t="s">
         <v>106</v>
@@ -70402,16 +70399,16 @@
         <v>285</v>
       </c>
       <c r="B286" t="s">
+        <v>434</v>
+      </c>
+      <c r="C286" t="s">
         <v>435</v>
-      </c>
-      <c r="C286" t="s">
-        <v>436</v>
       </c>
       <c r="D286">
         <v>235422856</v>
       </c>
       <c r="E286" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="F286" t="s">
         <v>178</v>
@@ -70588,7 +70585,7 @@
         <v>0</v>
       </c>
       <c r="BL286" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="BM286">
         <v>203344056</v>
@@ -70597,7 +70594,7 @@
         <v>82</v>
       </c>
       <c r="BO286" t="s">
-        <v>835</v>
+        <v>834</v>
       </c>
       <c r="BP286" t="s">
         <v>82</v>
@@ -70606,7 +70603,7 @@
         <v>111</v>
       </c>
       <c r="BR286" t="s">
-        <v>836</v>
+        <v>835</v>
       </c>
       <c r="BS286">
         <v>NaN</v>
@@ -70638,22 +70635,22 @@
         <v>286</v>
       </c>
       <c r="B287" t="s">
+        <v>434</v>
+      </c>
+      <c r="C287" t="s">
         <v>435</v>
-      </c>
-      <c r="C287" t="s">
-        <v>436</v>
       </c>
       <c r="D287">
         <v>235479615</v>
       </c>
       <c r="E287" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
       <c r="F287" t="s">
+        <v>292</v>
+      </c>
+      <c r="G287" t="s">
         <v>293</v>
-      </c>
-      <c r="G287" t="s">
-        <v>294</v>
       </c>
       <c r="H287">
         <v>8908924</v>
@@ -70833,22 +70830,22 @@
         <v>82</v>
       </c>
       <c r="BO287" t="s">
+        <v>837</v>
+      </c>
+      <c r="BP287" t="s">
+        <v>82</v>
+      </c>
+      <c r="BQ287" t="s">
+        <v>499</v>
+      </c>
+      <c r="BR287" t="s">
         <v>838</v>
-      </c>
-      <c r="BP287" t="s">
-        <v>82</v>
-      </c>
-      <c r="BQ287" t="s">
-        <v>500</v>
-      </c>
-      <c r="BR287" t="s">
-        <v>839</v>
       </c>
       <c r="BS287">
         <v>NaN</v>
       </c>
       <c r="BT287" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="BU287" t="s">
         <v>82</v>
@@ -70874,16 +70871,16 @@
         <v>287</v>
       </c>
       <c r="B288" t="s">
+        <v>434</v>
+      </c>
+      <c r="C288" t="s">
         <v>435</v>
-      </c>
-      <c r="C288" t="s">
-        <v>436</v>
       </c>
       <c r="D288">
         <v>235365247</v>
       </c>
       <c r="E288" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="F288" t="s">
         <v>138</v>
@@ -71069,22 +71066,22 @@
         <v>82</v>
       </c>
       <c r="BO288" t="s">
+        <v>840</v>
+      </c>
+      <c r="BP288" t="s">
+        <v>82</v>
+      </c>
+      <c r="BQ288" t="s">
+        <v>476</v>
+      </c>
+      <c r="BR288" t="s">
         <v>841</v>
-      </c>
-      <c r="BP288" t="s">
-        <v>82</v>
-      </c>
-      <c r="BQ288" t="s">
-        <v>477</v>
-      </c>
-      <c r="BR288" t="s">
-        <v>842</v>
       </c>
       <c r="BS288">
         <v>NaN</v>
       </c>
       <c r="BT288" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="BU288" t="s">
         <v>82</v>
@@ -71110,16 +71107,16 @@
         <v>288</v>
       </c>
       <c r="B289" t="s">
+        <v>434</v>
+      </c>
+      <c r="C289" t="s">
         <v>435</v>
-      </c>
-      <c r="C289" t="s">
-        <v>436</v>
       </c>
       <c r="D289">
         <v>235692700</v>
       </c>
       <c r="E289" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="F289" t="s">
         <v>138</v>
@@ -71296,7 +71293,7 @@
         <v>0</v>
       </c>
       <c r="BL289" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="BM289">
         <v>262724424</v>
@@ -71305,7 +71302,7 @@
         <v>82</v>
       </c>
       <c r="BO289" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="BP289" t="s">
         <v>82</v>
@@ -71314,13 +71311,13 @@
         <v>130</v>
       </c>
       <c r="BR289" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="BS289">
         <v>NaN</v>
       </c>
       <c r="BT289" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="BU289" t="s">
         <v>82</v>
@@ -71346,16 +71343,16 @@
         <v>289</v>
       </c>
       <c r="B290" t="s">
+        <v>434</v>
+      </c>
+      <c r="C290" t="s">
         <v>435</v>
-      </c>
-      <c r="C290" t="s">
-        <v>436</v>
       </c>
       <c r="D290">
         <v>235693024</v>
       </c>
       <c r="E290" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="F290" t="s">
         <v>94</v>
@@ -71532,7 +71529,7 @@
         <v>0</v>
       </c>
       <c r="BL290" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="BM290">
         <v>27872771</v>
@@ -71541,22 +71538,22 @@
         <v>82</v>
       </c>
       <c r="BO290" t="s">
+        <v>848</v>
+      </c>
+      <c r="BP290" t="s">
+        <v>82</v>
+      </c>
+      <c r="BQ290" t="s">
+        <v>354</v>
+      </c>
+      <c r="BR290" t="s">
         <v>849</v>
-      </c>
-      <c r="BP290" t="s">
-        <v>82</v>
-      </c>
-      <c r="BQ290" t="s">
-        <v>355</v>
-      </c>
-      <c r="BR290" t="s">
-        <v>850</v>
       </c>
       <c r="BS290">
         <v>NaN</v>
       </c>
       <c r="BT290" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="BU290" t="s">
         <v>82</v>
@@ -71582,16 +71579,16 @@
         <v>290</v>
       </c>
       <c r="B291" t="s">
+        <v>434</v>
+      </c>
+      <c r="C291" t="s">
         <v>435</v>
-      </c>
-      <c r="C291" t="s">
-        <v>436</v>
       </c>
       <c r="D291">
         <v>235460713</v>
       </c>
       <c r="E291" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="F291" t="s">
         <v>169</v>
@@ -71768,7 +71765,7 @@
         <v>0</v>
       </c>
       <c r="BL291" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="BM291">
         <v>263079454</v>
@@ -71777,16 +71774,16 @@
         <v>82</v>
       </c>
       <c r="BO291" t="s">
+        <v>852</v>
+      </c>
+      <c r="BP291" t="s">
+        <v>82</v>
+      </c>
+      <c r="BQ291" t="s">
+        <v>254</v>
+      </c>
+      <c r="BR291" t="s">
         <v>853</v>
-      </c>
-      <c r="BP291" t="s">
-        <v>82</v>
-      </c>
-      <c r="BQ291" t="s">
-        <v>255</v>
-      </c>
-      <c r="BR291" t="s">
-        <v>854</v>
       </c>
       <c r="BS291">
         <v>NaN</v>
@@ -71818,16 +71815,16 @@
         <v>291</v>
       </c>
       <c r="B292" t="s">
+        <v>854</v>
+      </c>
+      <c r="C292" t="s">
         <v>855</v>
-      </c>
-      <c r="C292" t="s">
-        <v>856</v>
       </c>
       <c r="D292">
         <v>235366052</v>
       </c>
       <c r="E292" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="F292" t="s">
         <v>81</v>
@@ -72054,22 +72051,22 @@
         <v>292</v>
       </c>
       <c r="B293" t="s">
+        <v>854</v>
+      </c>
+      <c r="C293" t="s">
         <v>855</v>
-      </c>
-      <c r="C293" t="s">
-        <v>856</v>
       </c>
       <c r="D293">
         <v>235723325</v>
       </c>
       <c r="E293" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="F293" t="s">
+        <v>292</v>
+      </c>
+      <c r="G293" t="s">
         <v>293</v>
-      </c>
-      <c r="G293" t="s">
-        <v>294</v>
       </c>
       <c r="H293">
         <v>8908924</v>
@@ -72099,7 +72096,7 @@
         <v>3</v>
       </c>
       <c r="Q293" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="R293">
         <v>4</v>
@@ -72240,7 +72237,7 @@
         <v>0</v>
       </c>
       <c r="BL293" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="BM293">
         <v>263339517</v>
@@ -72249,16 +72246,16 @@
         <v>82</v>
       </c>
       <c r="BO293" t="s">
+        <v>859</v>
+      </c>
+      <c r="BP293" t="s">
+        <v>82</v>
+      </c>
+      <c r="BQ293" t="s">
+        <v>318</v>
+      </c>
+      <c r="BR293" t="s">
         <v>860</v>
-      </c>
-      <c r="BP293" t="s">
-        <v>82</v>
-      </c>
-      <c r="BQ293" t="s">
-        <v>319</v>
-      </c>
-      <c r="BR293" t="s">
-        <v>861</v>
       </c>
       <c r="BS293">
         <v>NaN</v>
@@ -72290,16 +72287,16 @@
         <v>293</v>
       </c>
       <c r="B294" t="s">
+        <v>854</v>
+      </c>
+      <c r="C294" t="s">
         <v>855</v>
-      </c>
-      <c r="C294" t="s">
-        <v>856</v>
       </c>
       <c r="D294">
         <v>235748239</v>
       </c>
       <c r="E294" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="F294" t="s">
         <v>81</v>
@@ -72485,16 +72482,16 @@
         <v>82</v>
       </c>
       <c r="BO294" t="s">
+        <v>862</v>
+      </c>
+      <c r="BP294" t="s">
+        <v>82</v>
+      </c>
+      <c r="BQ294" t="s">
+        <v>590</v>
+      </c>
+      <c r="BR294" t="s">
         <v>863</v>
-      </c>
-      <c r="BP294" t="s">
-        <v>82</v>
-      </c>
-      <c r="BQ294" t="s">
-        <v>591</v>
-      </c>
-      <c r="BR294" t="s">
-        <v>864</v>
       </c>
       <c r="BS294">
         <v>NaN</v>
@@ -72526,16 +72523,16 @@
         <v>294</v>
       </c>
       <c r="B295" t="s">
+        <v>854</v>
+      </c>
+      <c r="C295" t="s">
         <v>855</v>
-      </c>
-      <c r="C295" t="s">
-        <v>856</v>
       </c>
       <c r="D295">
         <v>235702756</v>
       </c>
       <c r="E295" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="F295" t="s">
         <v>81</v>
@@ -72712,7 +72709,7 @@
         <v>0</v>
       </c>
       <c r="BL295" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="BM295">
         <v>243582933</v>
@@ -72721,7 +72718,7 @@
         <v>82</v>
       </c>
       <c r="BO295" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
       <c r="BP295" t="s">
         <v>82</v>
@@ -72730,7 +72727,7 @@
         <v>157</v>
       </c>
       <c r="BR295" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="BS295">
         <v>NaN</v>
@@ -72762,16 +72759,16 @@
         <v>295</v>
       </c>
       <c r="B296" t="s">
+        <v>854</v>
+      </c>
+      <c r="C296" t="s">
         <v>855</v>
-      </c>
-      <c r="C296" t="s">
-        <v>856</v>
       </c>
       <c r="D296">
         <v>235692922</v>
       </c>
       <c r="E296" t="s">
-        <v>869</v>
+        <v>868</v>
       </c>
       <c r="F296" t="s">
         <v>89</v>
@@ -72948,7 +72945,7 @@
         <v>0</v>
       </c>
       <c r="BL296" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
       <c r="BM296">
         <v>260376451</v>
@@ -72957,7 +72954,7 @@
         <v>82</v>
       </c>
       <c r="BO296" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="BP296" t="s">
         <v>82</v>
@@ -72966,7 +72963,7 @@
         <v>111</v>
       </c>
       <c r="BR296" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="BS296">
         <v>NaN</v>
@@ -72998,16 +72995,16 @@
         <v>296</v>
       </c>
       <c r="B297" t="s">
+        <v>854</v>
+      </c>
+      <c r="C297" t="s">
         <v>855</v>
-      </c>
-      <c r="C297" t="s">
-        <v>856</v>
       </c>
       <c r="D297">
         <v>235693057</v>
       </c>
       <c r="E297" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
       <c r="F297" t="s">
         <v>106</v>
@@ -73184,7 +73181,7 @@
         <v>0</v>
       </c>
       <c r="BL297" t="s">
-        <v>874</v>
+        <v>873</v>
       </c>
       <c r="BM297">
         <v>263227884</v>
@@ -73193,22 +73190,22 @@
         <v>82</v>
       </c>
       <c r="BO297" t="s">
+        <v>874</v>
+      </c>
+      <c r="BP297" t="s">
+        <v>82</v>
+      </c>
+      <c r="BQ297" t="s">
+        <v>354</v>
+      </c>
+      <c r="BR297" t="s">
         <v>875</v>
-      </c>
-      <c r="BP297" t="s">
-        <v>82</v>
-      </c>
-      <c r="BQ297" t="s">
-        <v>355</v>
-      </c>
-      <c r="BR297" t="s">
-        <v>876</v>
       </c>
       <c r="BS297">
         <v>NaN</v>
       </c>
       <c r="BT297" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="BU297" t="s">
         <v>82</v>
@@ -73234,22 +73231,22 @@
         <v>297</v>
       </c>
       <c r="B298" t="s">
+        <v>854</v>
+      </c>
+      <c r="C298" t="s">
         <v>855</v>
-      </c>
-      <c r="C298" t="s">
-        <v>856</v>
       </c>
       <c r="D298">
         <v>235751507</v>
       </c>
       <c r="E298" t="s">
-        <v>877</v>
+        <v>876</v>
       </c>
       <c r="F298" t="s">
+        <v>297</v>
+      </c>
+      <c r="G298" t="s">
         <v>298</v>
-      </c>
-      <c r="G298" t="s">
-        <v>299</v>
       </c>
       <c r="H298">
         <v>8908959</v>
@@ -73420,7 +73417,7 @@
         <v>0</v>
       </c>
       <c r="BL298" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
       <c r="BM298">
         <v>263398124</v>
@@ -73429,7 +73426,7 @@
         <v>82</v>
       </c>
       <c r="BO298" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="BP298" t="s">
         <v>82</v>
@@ -73438,13 +73435,13 @@
         <v>193</v>
       </c>
       <c r="BR298" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
       <c r="BS298">
         <v>NaN</v>
       </c>
       <c r="BT298" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="BU298" t="s">
         <v>82</v>
@@ -73470,22 +73467,22 @@
         <v>298</v>
       </c>
       <c r="B299" t="s">
+        <v>854</v>
+      </c>
+      <c r="C299" t="s">
         <v>855</v>
-      </c>
-      <c r="C299" t="s">
-        <v>856</v>
       </c>
       <c r="D299">
         <v>235706045</v>
       </c>
       <c r="E299" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="F299" t="s">
+        <v>292</v>
+      </c>
+      <c r="G299" t="s">
         <v>293</v>
-      </c>
-      <c r="G299" t="s">
-        <v>294</v>
       </c>
       <c r="H299">
         <v>8908924</v>
@@ -73515,7 +73512,7 @@
         <v>3</v>
       </c>
       <c r="Q299" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="R299">
         <v>4</v>
@@ -73656,7 +73653,7 @@
         <v>0</v>
       </c>
       <c r="BL299" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
       <c r="BM299">
         <v>263085607</v>
@@ -73665,7 +73662,7 @@
         <v>82</v>
       </c>
       <c r="BO299" t="s">
-        <v>883</v>
+        <v>882</v>
       </c>
       <c r="BP299" t="s">
         <v>82</v>
@@ -73674,13 +73671,13 @@
         <v>157</v>
       </c>
       <c r="BR299" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
       <c r="BS299">
         <v>NaN</v>
       </c>
       <c r="BT299" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="BU299" t="s">
         <v>82</v>
@@ -73706,22 +73703,22 @@
         <v>299</v>
       </c>
       <c r="B300" t="s">
+        <v>854</v>
+      </c>
+      <c r="C300" t="s">
         <v>855</v>
-      </c>
-      <c r="C300" t="s">
-        <v>856</v>
       </c>
       <c r="D300">
         <v>235727475</v>
       </c>
       <c r="E300" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="F300" t="s">
+        <v>292</v>
+      </c>
+      <c r="G300" t="s">
         <v>293</v>
-      </c>
-      <c r="G300" t="s">
-        <v>294</v>
       </c>
       <c r="H300">
         <v>8908924</v>
@@ -73892,7 +73889,7 @@
         <v>0</v>
       </c>
       <c r="BL300" t="s">
-        <v>886</v>
+        <v>885</v>
       </c>
       <c r="BM300">
         <v>263385045</v>
@@ -73901,7 +73898,7 @@
         <v>82</v>
       </c>
       <c r="BO300" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="BP300" t="s">
         <v>82</v>
@@ -73910,7 +73907,7 @@
         <v>175</v>
       </c>
       <c r="BR300" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="BS300">
         <v>NaN</v>
@@ -73942,16 +73939,16 @@
         <v>300</v>
       </c>
       <c r="B301" t="s">
+        <v>854</v>
+      </c>
+      <c r="C301" t="s">
         <v>855</v>
-      </c>
-      <c r="C301" t="s">
-        <v>856</v>
       </c>
       <c r="D301">
         <v>235397603</v>
       </c>
       <c r="E301" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="F301" t="s">
         <v>178</v>
@@ -74128,7 +74125,7 @@
         <v>0</v>
       </c>
       <c r="BL301" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="BM301">
         <v>263029939</v>
@@ -74137,22 +74134,22 @@
         <v>82</v>
       </c>
       <c r="BO301" t="s">
+        <v>890</v>
+      </c>
+      <c r="BP301" t="s">
+        <v>82</v>
+      </c>
+      <c r="BQ301" t="s">
+        <v>449</v>
+      </c>
+      <c r="BR301" t="s">
         <v>891</v>
-      </c>
-      <c r="BP301" t="s">
-        <v>82</v>
-      </c>
-      <c r="BQ301" t="s">
-        <v>450</v>
-      </c>
-      <c r="BR301" t="s">
-        <v>892</v>
       </c>
       <c r="BS301">
         <v>NaN</v>
       </c>
       <c r="BT301" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="BU301" t="s">
         <v>82</v>
